--- a/directory/gov/assets/xlsx/self_links.xlsx
+++ b/directory/gov/assets/xlsx/self_links.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA26"/>
+  <dimension ref="A1:AA60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -575,6 +575,7 @@
           <t>最高国家权力机关，行使国家立法权，官方网站发布法律、公报与常委会信息。</t>
         </is>
       </c>
+      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
           <t>人大,全国人大,国家立法</t>
@@ -590,6 +591,24 @@
           <t>https://www.npc.gov.cn</t>
         </is>
       </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -613,6 +632,7 @@
           <t>北京市人民代表大会常设机关，发布地方立法、监督与代表工作信息。</t>
         </is>
       </c>
+      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
           <t>人大,北京,直辖市</t>
@@ -628,6 +648,24 @@
           <t>https://www.bjrd.gov.cn</t>
         </is>
       </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr"/>
+      <c r="W3" t="inlineStr"/>
+      <c r="X3" t="inlineStr"/>
+      <c r="Y3" t="inlineStr"/>
+      <c r="Z3" t="inlineStr"/>
+      <c r="AA3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -651,6 +689,7 @@
           <t>上海市人民代表大会常设机关，地方立法与监督工作平台。</t>
         </is>
       </c>
+      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
           <t>人大,上海,直辖市</t>
@@ -666,6 +705,24 @@
           <t>https://www.shrd.gov.cn</t>
         </is>
       </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="inlineStr"/>
+      <c r="X4" t="inlineStr"/>
+      <c r="Y4" t="inlineStr"/>
+      <c r="Z4" t="inlineStr"/>
+      <c r="AA4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -689,6 +746,7 @@
           <t>天津市人民代表大会常设机关，发布地方性法规与监督信息。</t>
         </is>
       </c>
+      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
           <t>人大,天津,直辖市</t>
@@ -704,6 +762,24 @@
           <t>https://www.tjrd.gov.cn</t>
         </is>
       </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr"/>
+      <c r="X5" t="inlineStr"/>
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="inlineStr"/>
+      <c r="AA5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -727,6 +803,7 @@
           <t>重庆市人民代表大会常设机关，地方立法与代表工作平台。</t>
         </is>
       </c>
+      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
           <t>人大,重庆,直辖市</t>
@@ -742,6 +819,24 @@
           <t>https://www.cqrd.gov.cn</t>
         </is>
       </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="inlineStr"/>
+      <c r="X6" t="inlineStr"/>
+      <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="inlineStr"/>
+      <c r="AA6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -757,29 +852,48 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>广东省人民代表大会常务委员会</t>
+          <t>河北省人民代表大会常务委员会</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>广东省人民代表大会常设机关，发布地方性法规与监督信息。</t>
-        </is>
-      </c>
+          <t>河北省人民代表大会常设机关，发布地方立法、监督与代表履职信息。</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>人大,广东,省</t>
+          <t>人大,河北,省</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>访问官网 - www.rd.gd.cn</t>
+          <t>访问官网 - www.hbrd.gov.cn</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>https://www.rd.gd.cn</t>
-        </is>
-      </c>
+          <t>https://www.hbrd.gov.cn</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="inlineStr"/>
+      <c r="X7" t="inlineStr"/>
+      <c r="Y7" t="inlineStr"/>
+      <c r="Z7" t="inlineStr"/>
+      <c r="AA7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -795,29 +909,48 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>江苏省人民代表大会常务委员会</t>
+          <t>山西省人民代表大会常务委员会</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>江苏省人民代表大会常设机关，地方立法与监督工作平台。</t>
-        </is>
-      </c>
+          <t>山西省人民代表大会常设机关，发布地方性法规与监督工作信息。</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>人大,江苏,省</t>
+          <t>人大,山西,省</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>访问官网 - www.jsrd.gov.cn</t>
+          <t>访问官网 - www.sxpc.gov.cn</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>https://www.jsrd.gov.cn</t>
-        </is>
-      </c>
+          <t>https://www.sxpc.gov.cn</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr"/>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr"/>
+      <c r="W8" t="inlineStr"/>
+      <c r="X8" t="inlineStr"/>
+      <c r="Y8" t="inlineStr"/>
+      <c r="Z8" t="inlineStr"/>
+      <c r="AA8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -833,29 +966,48 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>浙江省人民代表大会常务委员会</t>
+          <t>辽宁省人民代表大会常务委员会</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>浙江省人民代表大会常设机关，发布地方性法规与代表信息。</t>
-        </is>
-      </c>
+          <t>辽宁省人民代表大会常设机关，发布地方立法与代表工作信息。</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>人大,浙江,省</t>
+          <t>人大,辽宁,省</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>访问官网 - www.zjrd.gov.cn</t>
+          <t>访问官网 - www.lnrd.gov.cn</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>https://www.zjrd.gov.cn</t>
-        </is>
-      </c>
+          <t>https://www.lnrd.gov.cn</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="inlineStr"/>
+      <c r="W9" t="inlineStr"/>
+      <c r="X9" t="inlineStr"/>
+      <c r="Y9" t="inlineStr"/>
+      <c r="Z9" t="inlineStr"/>
+      <c r="AA9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -871,29 +1023,48 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>山东省人民代表大会常务委员会</t>
+          <t>吉林省人民代表大会常务委员会</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>山东省人民代表大会常设机关，地方立法与监督工作平台。</t>
-        </is>
-      </c>
+          <t>吉林省人民代表大会常设机关，发布地方性法规与监督信息。</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>人大,山东,省</t>
+          <t>人大,吉林,省</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>访问官网 - www.sdrd.gov.cn</t>
+          <t>访问官网 - www.jlrd.gov.cn</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>https://www.sdrd.gov.cn</t>
-        </is>
-      </c>
+          <t>https://www.jlrd.gov.cn</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr"/>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="inlineStr"/>
+      <c r="W10" t="inlineStr"/>
+      <c r="X10" t="inlineStr"/>
+      <c r="Y10" t="inlineStr"/>
+      <c r="Z10" t="inlineStr"/>
+      <c r="AA10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -909,29 +1080,48 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>四川省人民代表大会常务委员会</t>
+          <t>黑龙江省人民代表大会常务委员会</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>四川省人民代表大会常设机关，发布地方性法规与监督信息。</t>
-        </is>
-      </c>
+          <t>黑龙江省人民代表大会常设机关，发布地方立法、监督与代表工作信息。</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>人大,四川,省</t>
+          <t>人大,黑龙江,省</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>访问官网 - www.scspc.gov.cn</t>
+          <t>访问官网 - www.hljrd.gov.cn</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>https://www.scspc.gov.cn</t>
-        </is>
-      </c>
+          <t>https://www.hljrd.gov.cn</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr"/>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="inlineStr"/>
+      <c r="W11" t="inlineStr"/>
+      <c r="X11" t="inlineStr"/>
+      <c r="Y11" t="inlineStr"/>
+      <c r="Z11" t="inlineStr"/>
+      <c r="AA11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -947,29 +1137,48 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>湖北省人民代表大会常务委员会</t>
+          <t>江苏省人民代表大会常务委员会</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>湖北省人民代表大会常设机关，地方立法与代表工作平台。</t>
-        </is>
-      </c>
+          <t>江苏省人民代表大会常设机关，地方立法与监督工作平台。</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>人大,湖北,省</t>
+          <t>人大,江苏,省</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>访问官网 - www.hppc.gov.cn</t>
+          <t>访问官网 - www.jsrd.gov.cn</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>https://www.hppc.gov.cn</t>
-        </is>
-      </c>
+          <t>https://www.jsrd.gov.cn</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr"/>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="inlineStr"/>
+      <c r="W12" t="inlineStr"/>
+      <c r="X12" t="inlineStr"/>
+      <c r="Y12" t="inlineStr"/>
+      <c r="Z12" t="inlineStr"/>
+      <c r="AA12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -985,29 +1194,48 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>河南省人民代表大会常务委员会</t>
+          <t>浙江省人民代表大会常务委员会</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>河南省人民代表大会常设机关，发布地方性法规与监督信息。</t>
-        </is>
-      </c>
+          <t>浙江省人民代表大会常设机关，发布地方性法规与代表信息。</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>人大,河南,省</t>
+          <t>人大,浙江,省</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>访问官网 - www.henanrd.gov.cn</t>
+          <t>访问官网 - www.zjrd.gov.cn</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>https://www.henanrd.gov.cn</t>
-        </is>
-      </c>
+          <t>https://www.zjrd.gov.cn</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="inlineStr"/>
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="inlineStr"/>
+      <c r="W13" t="inlineStr"/>
+      <c r="X13" t="inlineStr"/>
+      <c r="Y13" t="inlineStr"/>
+      <c r="Z13" t="inlineStr"/>
+      <c r="AA13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1015,7 +1243,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>国务院</t>
+          <t>省</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -1023,29 +1251,48 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>中华人民共和国中央人民政府（国务院）</t>
+          <t>安徽省人民代表大会常务委员会</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>国务院官方网站，国家政务总门户，发布政策法规与政务信息。</t>
-        </is>
-      </c>
+          <t>安徽省人民代表大会常设机关，发布地方立法与代表履职信息。</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>政务,国务院,中央政府</t>
+          <t>人大,安徽,省</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>访问官网 - www.gov.cn</t>
+          <t>访问官网 - www.ahrd.gov.cn</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>https://www.gov.cn</t>
-        </is>
-      </c>
+          <t>https://www.ahrd.gov.cn</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr"/>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="inlineStr"/>
+      <c r="W14" t="inlineStr"/>
+      <c r="X14" t="inlineStr"/>
+      <c r="Y14" t="inlineStr"/>
+      <c r="Z14" t="inlineStr"/>
+      <c r="AA14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -1053,7 +1300,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>国家平台</t>
+          <t>省</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -1061,29 +1308,48 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>国家政务服务平台</t>
+          <t>福建省人民代表大会常务委员会</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>全国统一政务服务平台，提供在线办事、政务服务与效能监督。</t>
-        </is>
-      </c>
+          <t>福建省人民代表大会常设机关，发布地方性法规与监督工作信息。</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>政务,服务平台,在线办事</t>
+          <t>人大,福建,省</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>访问官网 - gjzwfw.www.gov.cn</t>
+          <t>访问官网 - www.fjrd.gov.cn</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>https://gjzwfw.www.gov.cn</t>
-        </is>
-      </c>
+          <t>https://www.fjrd.gov.cn</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="inlineStr"/>
+      <c r="T15" t="inlineStr"/>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="inlineStr"/>
+      <c r="W15" t="inlineStr"/>
+      <c r="X15" t="inlineStr"/>
+      <c r="Y15" t="inlineStr"/>
+      <c r="Z15" t="inlineStr"/>
+      <c r="AA15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1091,7 +1357,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>组成部门</t>
+          <t>省</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -1099,29 +1365,48 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>国家发展和改革委员会</t>
+          <t>江西省人民代表大会常务委员会</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>宏观经济综合管理，拟订发展战略与规划。</t>
-        </is>
-      </c>
+          <t>江西省人民代表大会常设机关，发布地方立法与代表工作信息。</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>政务,发改委,宏观经济</t>
+          <t>人大,江西,省</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>访问官网 - www.ndrc.gov.cn</t>
+          <t>访问官网 - www.jxrd.gov.cn</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>https://www.ndrc.gov.cn</t>
-        </is>
-      </c>
+          <t>https://www.jxrd.gov.cn</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr"/>
+      <c r="S16" t="inlineStr"/>
+      <c r="T16" t="inlineStr"/>
+      <c r="U16" t="inlineStr"/>
+      <c r="V16" t="inlineStr"/>
+      <c r="W16" t="inlineStr"/>
+      <c r="X16" t="inlineStr"/>
+      <c r="Y16" t="inlineStr"/>
+      <c r="Z16" t="inlineStr"/>
+      <c r="AA16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1129,7 +1414,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>组成部门</t>
+          <t>省</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -1137,29 +1422,48 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>教育部</t>
+          <t>山东省人民代表大会常务委员会</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>主管教育事业与语言文字工作，发布教育政策。</t>
-        </is>
-      </c>
+          <t>山东省人民代表大会常设机关，地方立法与监督工作平台。</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>政务,教育,教育部</t>
+          <t>人大,山东,省</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>访问官网 - www.moe.gov.cn</t>
+          <t>访问官网 - www.sdrd.gov.cn</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>https://www.moe.gov.cn</t>
-        </is>
-      </c>
+          <t>https://www.sdrd.gov.cn</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr"/>
+      <c r="S17" t="inlineStr"/>
+      <c r="T17" t="inlineStr"/>
+      <c r="U17" t="inlineStr"/>
+      <c r="V17" t="inlineStr"/>
+      <c r="W17" t="inlineStr"/>
+      <c r="X17" t="inlineStr"/>
+      <c r="Y17" t="inlineStr"/>
+      <c r="Z17" t="inlineStr"/>
+      <c r="AA17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -1167,7 +1471,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>组成部门</t>
+          <t>省</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -1175,29 +1479,48 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>财政部</t>
+          <t>河南省人民代表大会常务委员会</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>主管国家财政收支与财税政策。</t>
-        </is>
-      </c>
+          <t>河南省人民代表大会常设机关，发布地方性法规与监督信息。</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>政务,财政,财政部</t>
+          <t>人大,河南,省</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>访问官网 - www.mof.gov.cn</t>
+          <t>访问官网 - www.henanrd.gov.cn</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>https://www.mof.gov.cn</t>
-        </is>
-      </c>
+          <t>https://www.henanrd.gov.cn</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr"/>
+      <c r="S18" t="inlineStr"/>
+      <c r="T18" t="inlineStr"/>
+      <c r="U18" t="inlineStr"/>
+      <c r="V18" t="inlineStr"/>
+      <c r="W18" t="inlineStr"/>
+      <c r="X18" t="inlineStr"/>
+      <c r="Y18" t="inlineStr"/>
+      <c r="Z18" t="inlineStr"/>
+      <c r="AA18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -1205,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>组成部门</t>
+          <t>省</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -1213,29 +1536,48 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>公安部</t>
+          <t>湖北省人民代表大会常务委员会</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>维护社会治安，主管公安工作。</t>
-        </is>
-      </c>
+          <t>湖北省人民代表大会常设机关，地方立法与代表工作平台。</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>政务,公安,公安部</t>
+          <t>人大,湖北,省</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>访问官网 - www.mps.gov.cn</t>
+          <t>访问官网 - www.hppc.gov.cn</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>https://www.mps.gov.cn</t>
-        </is>
-      </c>
+          <t>https://www.hppc.gov.cn</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr"/>
+      <c r="S19" t="inlineStr"/>
+      <c r="T19" t="inlineStr"/>
+      <c r="U19" t="inlineStr"/>
+      <c r="V19" t="inlineStr"/>
+      <c r="W19" t="inlineStr"/>
+      <c r="X19" t="inlineStr"/>
+      <c r="Y19" t="inlineStr"/>
+      <c r="Z19" t="inlineStr"/>
+      <c r="AA19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -1243,7 +1585,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>组成部门</t>
+          <t>省</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -1251,29 +1593,48 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>民政部</t>
+          <t>湖南省人民代表大会常务委员会</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>主管民政事务、社会救助与社会组织管理。</t>
-        </is>
-      </c>
+          <t>湖南省人民代表大会常设机关，发布地方性法规与监督信息。</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>政务,民政,民政部</t>
+          <t>人大,湖南,省</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>访问官网 - www.mca.gov.cn</t>
+          <t>访问官网 - www.hnrd.gov.cn</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>https://www.mca.gov.cn</t>
-        </is>
-      </c>
+          <t>https://www.hnrd.gov.cn</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="inlineStr"/>
+      <c r="S20" t="inlineStr"/>
+      <c r="T20" t="inlineStr"/>
+      <c r="U20" t="inlineStr"/>
+      <c r="V20" t="inlineStr"/>
+      <c r="W20" t="inlineStr"/>
+      <c r="X20" t="inlineStr"/>
+      <c r="Y20" t="inlineStr"/>
+      <c r="Z20" t="inlineStr"/>
+      <c r="AA20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -1281,7 +1642,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>组成部门</t>
+          <t>省</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -1289,29 +1650,48 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>司法部</t>
+          <t>广东省人民代表大会常务委员会</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>主管司法行政、法治建设与法律服务。</t>
-        </is>
-      </c>
+          <t>广东省人民代表大会常设机关，发布地方性法规与监督信息。</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
-          <t>政务,司法,司法部</t>
+          <t>人大,广东,省</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>访问官网 - www.moj.gov.cn</t>
+          <t>访问官网 - www.rd.gd.cn</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>https://www.moj.gov.cn</t>
-        </is>
-      </c>
+          <t>https://www.rd.gd.cn</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr"/>
+      <c r="R21" t="inlineStr"/>
+      <c r="S21" t="inlineStr"/>
+      <c r="T21" t="inlineStr"/>
+      <c r="U21" t="inlineStr"/>
+      <c r="V21" t="inlineStr"/>
+      <c r="W21" t="inlineStr"/>
+      <c r="X21" t="inlineStr"/>
+      <c r="Y21" t="inlineStr"/>
+      <c r="Z21" t="inlineStr"/>
+      <c r="AA21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -1319,7 +1699,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>组成部门</t>
+          <t>省</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -1327,29 +1707,48 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>人力资源和社会保障部</t>
+          <t>海南省人民代表大会常务委员会</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>主管就业、社保与人事人才工作。</t>
-        </is>
-      </c>
+          <t>海南省人民代表大会常设机关，发布地方立法、监督与代表工作信息。</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
-          <t>政务,人社,社保</t>
+          <t>人大,海南,省</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>访问官网 - www.mohrss.gov.cn</t>
+          <t>访问官网 - www.hainanpc.gov.cn</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>https://www.mohrss.gov.cn</t>
-        </is>
-      </c>
+          <t>https://www.hainanpc.gov.cn</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" t="inlineStr"/>
+      <c r="Q22" t="inlineStr"/>
+      <c r="R22" t="inlineStr"/>
+      <c r="S22" t="inlineStr"/>
+      <c r="T22" t="inlineStr"/>
+      <c r="U22" t="inlineStr"/>
+      <c r="V22" t="inlineStr"/>
+      <c r="W22" t="inlineStr"/>
+      <c r="X22" t="inlineStr"/>
+      <c r="Y22" t="inlineStr"/>
+      <c r="Z22" t="inlineStr"/>
+      <c r="AA22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -1357,7 +1756,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>组成部门</t>
+          <t>省</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -1365,29 +1764,48 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>自然资源部</t>
+          <t>四川省人民代表大会常务委员会</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>主管自然资源调查、规划与确权登记。</t>
-        </is>
-      </c>
+          <t>四川省人民代表大会常设机关，发布地方性法规与监督信息。</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
-          <t>政务,自然资源,国土</t>
+          <t>人大,四川,省</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>访问官网 - www.mnr.gov.cn</t>
+          <t>访问官网 - www.scspc.gov.cn</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>https://www.mnr.gov.cn</t>
-        </is>
-      </c>
+          <t>https://www.scspc.gov.cn</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" t="inlineStr"/>
+      <c r="Q23" t="inlineStr"/>
+      <c r="R23" t="inlineStr"/>
+      <c r="S23" t="inlineStr"/>
+      <c r="T23" t="inlineStr"/>
+      <c r="U23" t="inlineStr"/>
+      <c r="V23" t="inlineStr"/>
+      <c r="W23" t="inlineStr"/>
+      <c r="X23" t="inlineStr"/>
+      <c r="Y23" t="inlineStr"/>
+      <c r="Z23" t="inlineStr"/>
+      <c r="AA23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -1395,7 +1813,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>组成部门</t>
+          <t>省</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -1403,29 +1821,48 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>生态环境部</t>
+          <t>贵州省人民代表大会常务委员会</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>主管生态环境保护的监督管理。</t>
-        </is>
-      </c>
+          <t>贵州省人民代表大会常设机关，发布地方性法规与监督信息。</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
-          <t>政务,生态环境,环保</t>
+          <t>人大,贵州,省</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>访问官网 - www.mee.gov.cn</t>
+          <t>访问官网 - www.gzrd.gov.cn</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>https://www.mee.gov.cn</t>
-        </is>
-      </c>
+          <t>https://www.gzrd.gov.cn</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr"/>
+      <c r="R24" t="inlineStr"/>
+      <c r="S24" t="inlineStr"/>
+      <c r="T24" t="inlineStr"/>
+      <c r="U24" t="inlineStr"/>
+      <c r="V24" t="inlineStr"/>
+      <c r="W24" t="inlineStr"/>
+      <c r="X24" t="inlineStr"/>
+      <c r="Y24" t="inlineStr"/>
+      <c r="Z24" t="inlineStr"/>
+      <c r="AA24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -1433,7 +1870,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>组成部门</t>
+          <t>省</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -1441,29 +1878,48 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>交通运输部</t>
+          <t>云南省人民代表大会常务委员会</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>主管公路、水路、铁路等综合交通运输。</t>
-        </is>
-      </c>
+          <t>云南省人民代表大会常设机关，发布地方立法与代表履职信息。</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
-          <t>政务,交通,运输</t>
+          <t>人大,云南,省</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>访问官网 - www.mot.gov.cn</t>
+          <t>访问官网 - www.ynrd.gov.cn</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>https://www.mot.gov.cn</t>
-        </is>
-      </c>
+          <t>https://www.ynrd.gov.cn</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" t="inlineStr"/>
+      <c r="Q25" t="inlineStr"/>
+      <c r="R25" t="inlineStr"/>
+      <c r="S25" t="inlineStr"/>
+      <c r="T25" t="inlineStr"/>
+      <c r="U25" t="inlineStr"/>
+      <c r="V25" t="inlineStr"/>
+      <c r="W25" t="inlineStr"/>
+      <c r="X25" t="inlineStr"/>
+      <c r="Y25" t="inlineStr"/>
+      <c r="Z25" t="inlineStr"/>
+      <c r="AA25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -1471,37 +1927,1994 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
+          <t>省</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>1</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>陕西省人民代表大会常务委员会</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>陕西省人民代表大会常设机关，发布地方性法规与监督工作信息。</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>人大,陕西,省</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>访问官网 - www.sxrd.gov.cn</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>https://www.sxrd.gov.cn</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="inlineStr"/>
+      <c r="P26" t="inlineStr"/>
+      <c r="Q26" t="inlineStr"/>
+      <c r="R26" t="inlineStr"/>
+      <c r="S26" t="inlineStr"/>
+      <c r="T26" t="inlineStr"/>
+      <c r="U26" t="inlineStr"/>
+      <c r="V26" t="inlineStr"/>
+      <c r="W26" t="inlineStr"/>
+      <c r="X26" t="inlineStr"/>
+      <c r="Y26" t="inlineStr"/>
+      <c r="Z26" t="inlineStr"/>
+      <c r="AA26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>25</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>省</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>1</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>甘肃省人民代表大会常务委员会</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>甘肃省人民代表大会常设机关，发布地方立法与代表工作信息。</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>人大,甘肃,省</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>访问官网 - www.gsrdw.gov.cn</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>https://www.gsrdw.gov.cn</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="O27" t="inlineStr"/>
+      <c r="P27" t="inlineStr"/>
+      <c r="Q27" t="inlineStr"/>
+      <c r="R27" t="inlineStr"/>
+      <c r="S27" t="inlineStr"/>
+      <c r="T27" t="inlineStr"/>
+      <c r="U27" t="inlineStr"/>
+      <c r="V27" t="inlineStr"/>
+      <c r="W27" t="inlineStr"/>
+      <c r="X27" t="inlineStr"/>
+      <c r="Y27" t="inlineStr"/>
+      <c r="Z27" t="inlineStr"/>
+      <c r="AA27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>26</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>省</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>1</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>青海省人民代表大会常务委员会</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>青海省人民代表大会常设机关，发布地方性法规与监督信息。</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>人大,青海,省</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>访问官网 - www.qhrd.gov.cn</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>https://www.qhrd.gov.cn</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="O28" t="inlineStr"/>
+      <c r="P28" t="inlineStr"/>
+      <c r="Q28" t="inlineStr"/>
+      <c r="R28" t="inlineStr"/>
+      <c r="S28" t="inlineStr"/>
+      <c r="T28" t="inlineStr"/>
+      <c r="U28" t="inlineStr"/>
+      <c r="V28" t="inlineStr"/>
+      <c r="W28" t="inlineStr"/>
+      <c r="X28" t="inlineStr"/>
+      <c r="Y28" t="inlineStr"/>
+      <c r="Z28" t="inlineStr"/>
+      <c r="AA28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>27</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>自治区</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>1</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>内蒙古自治区人民代表大会常务委员会</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>内蒙古自治区人民代表大会常设机关，发布地方立法、监督与代表工作信息。</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>人大,内蒙古,自治区</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>访问官网 - www.nmgrd.gov.cn</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>https://www.nmgrd.gov.cn</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="O29" t="inlineStr"/>
+      <c r="P29" t="inlineStr"/>
+      <c r="Q29" t="inlineStr"/>
+      <c r="R29" t="inlineStr"/>
+      <c r="S29" t="inlineStr"/>
+      <c r="T29" t="inlineStr"/>
+      <c r="U29" t="inlineStr"/>
+      <c r="V29" t="inlineStr"/>
+      <c r="W29" t="inlineStr"/>
+      <c r="X29" t="inlineStr"/>
+      <c r="Y29" t="inlineStr"/>
+      <c r="Z29" t="inlineStr"/>
+      <c r="AA29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>28</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>自治区</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>1</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>广西壮族自治区人民代表大会常务委员会</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>广西壮族自治区人民代表大会常设机关，发布地方立法与代表履职信息。</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>人大,广西,自治区</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>访问官网 - www.gxrd.gov.cn</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>https://www.gxrd.gov.cn</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="O30" t="inlineStr"/>
+      <c r="P30" t="inlineStr"/>
+      <c r="Q30" t="inlineStr"/>
+      <c r="R30" t="inlineStr"/>
+      <c r="S30" t="inlineStr"/>
+      <c r="T30" t="inlineStr"/>
+      <c r="U30" t="inlineStr"/>
+      <c r="V30" t="inlineStr"/>
+      <c r="W30" t="inlineStr"/>
+      <c r="X30" t="inlineStr"/>
+      <c r="Y30" t="inlineStr"/>
+      <c r="Z30" t="inlineStr"/>
+      <c r="AA30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>29</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>自治区</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>1</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>西藏自治区人民代表大会常务委员会</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>西藏自治区人民代表大会常设机关，发布地方立法与监督信息。</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>人大,西藏,自治区</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>访问官网 - www.xizangrd.gov.cn</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>https://www.xizangrd.gov.cn</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="O31" t="inlineStr"/>
+      <c r="P31" t="inlineStr"/>
+      <c r="Q31" t="inlineStr"/>
+      <c r="R31" t="inlineStr"/>
+      <c r="S31" t="inlineStr"/>
+      <c r="T31" t="inlineStr"/>
+      <c r="U31" t="inlineStr"/>
+      <c r="V31" t="inlineStr"/>
+      <c r="W31" t="inlineStr"/>
+      <c r="X31" t="inlineStr"/>
+      <c r="Y31" t="inlineStr"/>
+      <c r="Z31" t="inlineStr"/>
+      <c r="AA31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>30</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>自治区</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>1</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>宁夏回族自治区人民代表大会常务委员会</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>宁夏回族自治区人民代表大会常设机关，发布地方性法规与代表工作信息。</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>人大,宁夏,自治区</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>访问官网 - www.nxrd.gov.cn</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>https://www.nxrd.gov.cn</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+      <c r="O32" t="inlineStr"/>
+      <c r="P32" t="inlineStr"/>
+      <c r="Q32" t="inlineStr"/>
+      <c r="R32" t="inlineStr"/>
+      <c r="S32" t="inlineStr"/>
+      <c r="T32" t="inlineStr"/>
+      <c r="U32" t="inlineStr"/>
+      <c r="V32" t="inlineStr"/>
+      <c r="W32" t="inlineStr"/>
+      <c r="X32" t="inlineStr"/>
+      <c r="Y32" t="inlineStr"/>
+      <c r="Z32" t="inlineStr"/>
+      <c r="AA32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>31</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>自治区</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>1</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>新疆维吾尔自治区人民代表大会常务委员会</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>新疆维吾尔自治区人民代表大会常设机关，发布地方立法、监督与代表工作信息。</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>人大,新疆,自治区</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>访问官网 - www.xjpcsc.gov.cn</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>https://www.xjpcsc.gov.cn</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+      <c r="O33" t="inlineStr"/>
+      <c r="P33" t="inlineStr"/>
+      <c r="Q33" t="inlineStr"/>
+      <c r="R33" t="inlineStr"/>
+      <c r="S33" t="inlineStr"/>
+      <c r="T33" t="inlineStr"/>
+      <c r="U33" t="inlineStr"/>
+      <c r="V33" t="inlineStr"/>
+      <c r="W33" t="inlineStr"/>
+      <c r="X33" t="inlineStr"/>
+      <c r="Y33" t="inlineStr"/>
+      <c r="Z33" t="inlineStr"/>
+      <c r="AA33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>32</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>国务院</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>1</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>中华人民共和国中央人民政府（国务院）</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>国务院官方网站，国家政务总门户，发布政策法规与政务信息。</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>政务,国务院,中央政府</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>访问官网 - www.gov.cn</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>https://www.gov.cn</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="O34" t="inlineStr"/>
+      <c r="P34" t="inlineStr"/>
+      <c r="Q34" t="inlineStr"/>
+      <c r="R34" t="inlineStr"/>
+      <c r="S34" t="inlineStr"/>
+      <c r="T34" t="inlineStr"/>
+      <c r="U34" t="inlineStr"/>
+      <c r="V34" t="inlineStr"/>
+      <c r="W34" t="inlineStr"/>
+      <c r="X34" t="inlineStr"/>
+      <c r="Y34" t="inlineStr"/>
+      <c r="Z34" t="inlineStr"/>
+      <c r="AA34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>33</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>国家平台</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>1</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>国家政务服务平台</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>全国统一政务服务平台，提供在线办事、政务服务与效能监督。</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>政务,服务平台,在线办事</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>访问官网 - gjzwfw.www.gov.cn</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>https://gjzwfw.www.gov.cn</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
+      <c r="O35" t="inlineStr"/>
+      <c r="P35" t="inlineStr"/>
+      <c r="Q35" t="inlineStr"/>
+      <c r="R35" t="inlineStr"/>
+      <c r="S35" t="inlineStr"/>
+      <c r="T35" t="inlineStr"/>
+      <c r="U35" t="inlineStr"/>
+      <c r="V35" t="inlineStr"/>
+      <c r="W35" t="inlineStr"/>
+      <c r="X35" t="inlineStr"/>
+      <c r="Y35" t="inlineStr"/>
+      <c r="Z35" t="inlineStr"/>
+      <c r="AA35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>34</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
           <t>组成部门</t>
         </is>
       </c>
-      <c r="C26" t="n">
-        <v>1</v>
-      </c>
-      <c r="D26" t="inlineStr">
+      <c r="C36" t="n">
+        <v>1</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>外交部</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>主管外交事务，发布外交政策、双边关系与国际交往信息。</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>政务,外交,外交部</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>访问官网 - www.mfa.gov.cn</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>https://www.mfa.gov.cn</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
+      <c r="O36" t="inlineStr"/>
+      <c r="P36" t="inlineStr"/>
+      <c r="Q36" t="inlineStr"/>
+      <c r="R36" t="inlineStr"/>
+      <c r="S36" t="inlineStr"/>
+      <c r="T36" t="inlineStr"/>
+      <c r="U36" t="inlineStr"/>
+      <c r="V36" t="inlineStr"/>
+      <c r="W36" t="inlineStr"/>
+      <c r="X36" t="inlineStr"/>
+      <c r="Y36" t="inlineStr"/>
+      <c r="Z36" t="inlineStr"/>
+      <c r="AA36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>35</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>组成部门</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>1</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>国防部</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>中华人民共和国国防部，发布国防政策、军队建设与权威军事信息。</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>政务,国防,国防部</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>访问官网 - www.mod.gov.cn</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>https://www.mod.gov.cn</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
+      <c r="O37" t="inlineStr"/>
+      <c r="P37" t="inlineStr"/>
+      <c r="Q37" t="inlineStr"/>
+      <c r="R37" t="inlineStr"/>
+      <c r="S37" t="inlineStr"/>
+      <c r="T37" t="inlineStr"/>
+      <c r="U37" t="inlineStr"/>
+      <c r="V37" t="inlineStr"/>
+      <c r="W37" t="inlineStr"/>
+      <c r="X37" t="inlineStr"/>
+      <c r="Y37" t="inlineStr"/>
+      <c r="Z37" t="inlineStr"/>
+      <c r="AA37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>36</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>组成部门</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>1</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>国家发展和改革委员会</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>宏观经济综合管理，拟订发展战略与规划。</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>政务,发改委,宏观经济</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>访问官网 - www.ndrc.gov.cn</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>https://www.ndrc.gov.cn</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
+      <c r="O38" t="inlineStr"/>
+      <c r="P38" t="inlineStr"/>
+      <c r="Q38" t="inlineStr"/>
+      <c r="R38" t="inlineStr"/>
+      <c r="S38" t="inlineStr"/>
+      <c r="T38" t="inlineStr"/>
+      <c r="U38" t="inlineStr"/>
+      <c r="V38" t="inlineStr"/>
+      <c r="W38" t="inlineStr"/>
+      <c r="X38" t="inlineStr"/>
+      <c r="Y38" t="inlineStr"/>
+      <c r="Z38" t="inlineStr"/>
+      <c r="AA38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>37</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>组成部门</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>1</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>教育部</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>主管教育事业与语言文字工作，发布教育政策。</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>政务,教育,教育部</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>访问官网 - www.moe.gov.cn</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>https://www.moe.gov.cn</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
+      <c r="O39" t="inlineStr"/>
+      <c r="P39" t="inlineStr"/>
+      <c r="Q39" t="inlineStr"/>
+      <c r="R39" t="inlineStr"/>
+      <c r="S39" t="inlineStr"/>
+      <c r="T39" t="inlineStr"/>
+      <c r="U39" t="inlineStr"/>
+      <c r="V39" t="inlineStr"/>
+      <c r="W39" t="inlineStr"/>
+      <c r="X39" t="inlineStr"/>
+      <c r="Y39" t="inlineStr"/>
+      <c r="Z39" t="inlineStr"/>
+      <c r="AA39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>38</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>组成部门</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>1</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>科学技术部</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>主管科技发展与创新，发布科技政策与研发计划信息。</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>政务,科技,科技部</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>访问官网 - www.most.gov.cn</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>https://www.most.gov.cn</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
+      <c r="O40" t="inlineStr"/>
+      <c r="P40" t="inlineStr"/>
+      <c r="Q40" t="inlineStr"/>
+      <c r="R40" t="inlineStr"/>
+      <c r="S40" t="inlineStr"/>
+      <c r="T40" t="inlineStr"/>
+      <c r="U40" t="inlineStr"/>
+      <c r="V40" t="inlineStr"/>
+      <c r="W40" t="inlineStr"/>
+      <c r="X40" t="inlineStr"/>
+      <c r="Y40" t="inlineStr"/>
+      <c r="Z40" t="inlineStr"/>
+      <c r="AA40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>39</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>组成部门</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>1</v>
+      </c>
+      <c r="D41" t="inlineStr">
         <is>
           <t>工业和信息化部</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="E41" t="inlineStr">
         <is>
           <t>主管工业与信息化产业发展与行业管理。</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr">
         <is>
           <t>政务,工信,信息化</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
+      <c r="H41" t="inlineStr">
         <is>
           <t>访问官网 - www.miit.gov.cn</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
+      <c r="I41" t="inlineStr">
         <is>
           <t>https://www.miit.gov.cn</t>
         </is>
       </c>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
+      <c r="O41" t="inlineStr"/>
+      <c r="P41" t="inlineStr"/>
+      <c r="Q41" t="inlineStr"/>
+      <c r="R41" t="inlineStr"/>
+      <c r="S41" t="inlineStr"/>
+      <c r="T41" t="inlineStr"/>
+      <c r="U41" t="inlineStr"/>
+      <c r="V41" t="inlineStr"/>
+      <c r="W41" t="inlineStr"/>
+      <c r="X41" t="inlineStr"/>
+      <c r="Y41" t="inlineStr"/>
+      <c r="Z41" t="inlineStr"/>
+      <c r="AA41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>40</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>组成部门</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>1</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>国家民族事务委员会</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>主管民族事务与民族团结进步工作，发布民族政策信息。</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>政务,民委,民族事务</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>访问官网 - www.neac.gov.cn</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>https://www.neac.gov.cn</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
+      <c r="O42" t="inlineStr"/>
+      <c r="P42" t="inlineStr"/>
+      <c r="Q42" t="inlineStr"/>
+      <c r="R42" t="inlineStr"/>
+      <c r="S42" t="inlineStr"/>
+      <c r="T42" t="inlineStr"/>
+      <c r="U42" t="inlineStr"/>
+      <c r="V42" t="inlineStr"/>
+      <c r="W42" t="inlineStr"/>
+      <c r="X42" t="inlineStr"/>
+      <c r="Y42" t="inlineStr"/>
+      <c r="Z42" t="inlineStr"/>
+      <c r="AA42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>41</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>组成部门</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>1</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>公安部</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>维护社会治安，主管公安工作。</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr"/>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>政务,公安,公安部</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>访问官网 - www.mps.gov.cn</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>https://www.mps.gov.cn</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
+      <c r="O43" t="inlineStr"/>
+      <c r="P43" t="inlineStr"/>
+      <c r="Q43" t="inlineStr"/>
+      <c r="R43" t="inlineStr"/>
+      <c r="S43" t="inlineStr"/>
+      <c r="T43" t="inlineStr"/>
+      <c r="U43" t="inlineStr"/>
+      <c r="V43" t="inlineStr"/>
+      <c r="W43" t="inlineStr"/>
+      <c r="X43" t="inlineStr"/>
+      <c r="Y43" t="inlineStr"/>
+      <c r="Z43" t="inlineStr"/>
+      <c r="AA43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>42</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>组成部门</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>1</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>民政部</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>主管民政事务、社会救助与社会组织管理。</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr"/>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>政务,民政,民政部</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>访问官网 - www.mca.gov.cn</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>https://www.mca.gov.cn</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
+      <c r="O44" t="inlineStr"/>
+      <c r="P44" t="inlineStr"/>
+      <c r="Q44" t="inlineStr"/>
+      <c r="R44" t="inlineStr"/>
+      <c r="S44" t="inlineStr"/>
+      <c r="T44" t="inlineStr"/>
+      <c r="U44" t="inlineStr"/>
+      <c r="V44" t="inlineStr"/>
+      <c r="W44" t="inlineStr"/>
+      <c r="X44" t="inlineStr"/>
+      <c r="Y44" t="inlineStr"/>
+      <c r="Z44" t="inlineStr"/>
+      <c r="AA44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>43</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>组成部门</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>1</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>司法部</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>主管司法行政、法治建设与法律服务。</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr"/>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>政务,司法,司法部</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>访问官网 - www.moj.gov.cn</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>https://www.moj.gov.cn</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
+      <c r="O45" t="inlineStr"/>
+      <c r="P45" t="inlineStr"/>
+      <c r="Q45" t="inlineStr"/>
+      <c r="R45" t="inlineStr"/>
+      <c r="S45" t="inlineStr"/>
+      <c r="T45" t="inlineStr"/>
+      <c r="U45" t="inlineStr"/>
+      <c r="V45" t="inlineStr"/>
+      <c r="W45" t="inlineStr"/>
+      <c r="X45" t="inlineStr"/>
+      <c r="Y45" t="inlineStr"/>
+      <c r="Z45" t="inlineStr"/>
+      <c r="AA45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>44</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>组成部门</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>1</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>财政部</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>主管国家财政收支与财税政策。</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr"/>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>政务,财政,财政部</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>访问官网 - www.mof.gov.cn</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>https://www.mof.gov.cn</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
+      <c r="O46" t="inlineStr"/>
+      <c r="P46" t="inlineStr"/>
+      <c r="Q46" t="inlineStr"/>
+      <c r="R46" t="inlineStr"/>
+      <c r="S46" t="inlineStr"/>
+      <c r="T46" t="inlineStr"/>
+      <c r="U46" t="inlineStr"/>
+      <c r="V46" t="inlineStr"/>
+      <c r="W46" t="inlineStr"/>
+      <c r="X46" t="inlineStr"/>
+      <c r="Y46" t="inlineStr"/>
+      <c r="Z46" t="inlineStr"/>
+      <c r="AA46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>45</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>组成部门</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>1</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>人力资源和社会保障部</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>主管就业、社保与人事人才工作。</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr"/>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>政务,人社,社保</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>访问官网 - www.mohrss.gov.cn</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>https://www.mohrss.gov.cn</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
+      <c r="O47" t="inlineStr"/>
+      <c r="P47" t="inlineStr"/>
+      <c r="Q47" t="inlineStr"/>
+      <c r="R47" t="inlineStr"/>
+      <c r="S47" t="inlineStr"/>
+      <c r="T47" t="inlineStr"/>
+      <c r="U47" t="inlineStr"/>
+      <c r="V47" t="inlineStr"/>
+      <c r="W47" t="inlineStr"/>
+      <c r="X47" t="inlineStr"/>
+      <c r="Y47" t="inlineStr"/>
+      <c r="Z47" t="inlineStr"/>
+      <c r="AA47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>46</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>组成部门</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>1</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>自然资源部</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>主管自然资源调查、规划与确权登记。</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr"/>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>政务,自然资源,国土</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>访问官网 - www.mnr.gov.cn</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>https://www.mnr.gov.cn</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
+      <c r="O48" t="inlineStr"/>
+      <c r="P48" t="inlineStr"/>
+      <c r="Q48" t="inlineStr"/>
+      <c r="R48" t="inlineStr"/>
+      <c r="S48" t="inlineStr"/>
+      <c r="T48" t="inlineStr"/>
+      <c r="U48" t="inlineStr"/>
+      <c r="V48" t="inlineStr"/>
+      <c r="W48" t="inlineStr"/>
+      <c r="X48" t="inlineStr"/>
+      <c r="Y48" t="inlineStr"/>
+      <c r="Z48" t="inlineStr"/>
+      <c r="AA48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>47</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>组成部门</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>1</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>生态环境部</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>主管生态环境保护的监督管理。</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr"/>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>政务,生态环境,环保</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>访问官网 - www.mee.gov.cn</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>https://www.mee.gov.cn</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
+      <c r="O49" t="inlineStr"/>
+      <c r="P49" t="inlineStr"/>
+      <c r="Q49" t="inlineStr"/>
+      <c r="R49" t="inlineStr"/>
+      <c r="S49" t="inlineStr"/>
+      <c r="T49" t="inlineStr"/>
+      <c r="U49" t="inlineStr"/>
+      <c r="V49" t="inlineStr"/>
+      <c r="W49" t="inlineStr"/>
+      <c r="X49" t="inlineStr"/>
+      <c r="Y49" t="inlineStr"/>
+      <c r="Z49" t="inlineStr"/>
+      <c r="AA49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>48</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>组成部门</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>1</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>住房和城乡建设部</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>主管住房保障与城乡建设，发布建筑市场与市政建设政策。</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr"/>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>政务,住建,城乡建设</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>访问官网 - www.mohurd.gov.cn</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>https://www.mohurd.gov.cn</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
+      <c r="O50" t="inlineStr"/>
+      <c r="P50" t="inlineStr"/>
+      <c r="Q50" t="inlineStr"/>
+      <c r="R50" t="inlineStr"/>
+      <c r="S50" t="inlineStr"/>
+      <c r="T50" t="inlineStr"/>
+      <c r="U50" t="inlineStr"/>
+      <c r="V50" t="inlineStr"/>
+      <c r="W50" t="inlineStr"/>
+      <c r="X50" t="inlineStr"/>
+      <c r="Y50" t="inlineStr"/>
+      <c r="Z50" t="inlineStr"/>
+      <c r="AA50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>49</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>组成部门</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>1</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>交通运输部</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>主管公路、水路、铁路等综合交通运输。</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr"/>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>政务,交通,运输</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>访问官网 - www.mot.gov.cn</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>https://www.mot.gov.cn</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
+      <c r="O51" t="inlineStr"/>
+      <c r="P51" t="inlineStr"/>
+      <c r="Q51" t="inlineStr"/>
+      <c r="R51" t="inlineStr"/>
+      <c r="S51" t="inlineStr"/>
+      <c r="T51" t="inlineStr"/>
+      <c r="U51" t="inlineStr"/>
+      <c r="V51" t="inlineStr"/>
+      <c r="W51" t="inlineStr"/>
+      <c r="X51" t="inlineStr"/>
+      <c r="Y51" t="inlineStr"/>
+      <c r="Z51" t="inlineStr"/>
+      <c r="AA51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>50</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>组成部门</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>1</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>水利部</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>主管水资源管理与水利建设，发布防汛抗旱与河湖治理信息。</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr"/>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>政务,水利,水资源</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>访问官网 - www.mwr.gov.cn</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>https://www.mwr.gov.cn</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
+      <c r="O52" t="inlineStr"/>
+      <c r="P52" t="inlineStr"/>
+      <c r="Q52" t="inlineStr"/>
+      <c r="R52" t="inlineStr"/>
+      <c r="S52" t="inlineStr"/>
+      <c r="T52" t="inlineStr"/>
+      <c r="U52" t="inlineStr"/>
+      <c r="V52" t="inlineStr"/>
+      <c r="W52" t="inlineStr"/>
+      <c r="X52" t="inlineStr"/>
+      <c r="Y52" t="inlineStr"/>
+      <c r="Z52" t="inlineStr"/>
+      <c r="AA52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>51</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>组成部门</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>1</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>农业农村部</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>主管农业农村发展，发布乡村振兴、农业政策与农技信息。</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr"/>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>政务,农业,农业农村</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>访问官网 - www.moa.gov.cn</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>https://www.moa.gov.cn</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
+      <c r="O53" t="inlineStr"/>
+      <c r="P53" t="inlineStr"/>
+      <c r="Q53" t="inlineStr"/>
+      <c r="R53" t="inlineStr"/>
+      <c r="S53" t="inlineStr"/>
+      <c r="T53" t="inlineStr"/>
+      <c r="U53" t="inlineStr"/>
+      <c r="V53" t="inlineStr"/>
+      <c r="W53" t="inlineStr"/>
+      <c r="X53" t="inlineStr"/>
+      <c r="Y53" t="inlineStr"/>
+      <c r="Z53" t="inlineStr"/>
+      <c r="AA53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>52</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>组成部门</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>1</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>商务部</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>主管国内外贸易与国际经贸合作，发布商务政策与市场信息。</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr"/>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>政务,商务,对外贸易</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>访问官网 - www.mofcom.gov.cn</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>https://www.mofcom.gov.cn</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
+      <c r="O54" t="inlineStr"/>
+      <c r="P54" t="inlineStr"/>
+      <c r="Q54" t="inlineStr"/>
+      <c r="R54" t="inlineStr"/>
+      <c r="S54" t="inlineStr"/>
+      <c r="T54" t="inlineStr"/>
+      <c r="U54" t="inlineStr"/>
+      <c r="V54" t="inlineStr"/>
+      <c r="W54" t="inlineStr"/>
+      <c r="X54" t="inlineStr"/>
+      <c r="Y54" t="inlineStr"/>
+      <c r="Z54" t="inlineStr"/>
+      <c r="AA54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>53</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>组成部门</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>1</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>文化和旅游部</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>主管文化事业与旅游发展，发布文旅政策与公共服务信息。</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr"/>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>政务,文旅,文化旅游</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>访问官网 - www.mct.gov.cn</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>https://www.mct.gov.cn</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
+      <c r="O55" t="inlineStr"/>
+      <c r="P55" t="inlineStr"/>
+      <c r="Q55" t="inlineStr"/>
+      <c r="R55" t="inlineStr"/>
+      <c r="S55" t="inlineStr"/>
+      <c r="T55" t="inlineStr"/>
+      <c r="U55" t="inlineStr"/>
+      <c r="V55" t="inlineStr"/>
+      <c r="W55" t="inlineStr"/>
+      <c r="X55" t="inlineStr"/>
+      <c r="Y55" t="inlineStr"/>
+      <c r="Z55" t="inlineStr"/>
+      <c r="AA55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>54</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>组成部门</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>1</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>国家卫生健康委员会</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>主管国民健康与医疗卫生，发布卫生政策与健康服务信息。</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr"/>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>政务,卫健,卫生健康</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>访问官网 - www.nhc.gov.cn</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>https://www.nhc.gov.cn</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
+      <c r="O56" t="inlineStr"/>
+      <c r="P56" t="inlineStr"/>
+      <c r="Q56" t="inlineStr"/>
+      <c r="R56" t="inlineStr"/>
+      <c r="S56" t="inlineStr"/>
+      <c r="T56" t="inlineStr"/>
+      <c r="U56" t="inlineStr"/>
+      <c r="V56" t="inlineStr"/>
+      <c r="W56" t="inlineStr"/>
+      <c r="X56" t="inlineStr"/>
+      <c r="Y56" t="inlineStr"/>
+      <c r="Z56" t="inlineStr"/>
+      <c r="AA56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>55</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>组成部门</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>1</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>退役军人事务部</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>主管退役军人优抚安置与服务保障，维护军人军属权益。</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr"/>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>政务,退役军人,优抚安置</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>访问官网 - www.mva.gov.cn</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>https://www.mva.gov.cn</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
+      <c r="O57" t="inlineStr"/>
+      <c r="P57" t="inlineStr"/>
+      <c r="Q57" t="inlineStr"/>
+      <c r="R57" t="inlineStr"/>
+      <c r="S57" t="inlineStr"/>
+      <c r="T57" t="inlineStr"/>
+      <c r="U57" t="inlineStr"/>
+      <c r="V57" t="inlineStr"/>
+      <c r="W57" t="inlineStr"/>
+      <c r="X57" t="inlineStr"/>
+      <c r="Y57" t="inlineStr"/>
+      <c r="Z57" t="inlineStr"/>
+      <c r="AA57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>56</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>组成部门</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>1</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>应急管理部</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>主管安全生产与应急救援，发布防灾减灾与事故处置信息。</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr"/>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>政务,应急,安全生产</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>访问官网 - www.mem.gov.cn</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>https://www.mem.gov.cn</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
+      <c r="O58" t="inlineStr"/>
+      <c r="P58" t="inlineStr"/>
+      <c r="Q58" t="inlineStr"/>
+      <c r="R58" t="inlineStr"/>
+      <c r="S58" t="inlineStr"/>
+      <c r="T58" t="inlineStr"/>
+      <c r="U58" t="inlineStr"/>
+      <c r="V58" t="inlineStr"/>
+      <c r="W58" t="inlineStr"/>
+      <c r="X58" t="inlineStr"/>
+      <c r="Y58" t="inlineStr"/>
+      <c r="Z58" t="inlineStr"/>
+      <c r="AA58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>57</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>组成部门</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>1</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>中国人民银行</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>中央银行，制定货币政策，维护金融稳定与人民币管理。</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr"/>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>政务,央行,货币政策</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>访问官网 - www.pbc.gov.cn</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>https://www.pbc.gov.cn</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
+      <c r="O59" t="inlineStr"/>
+      <c r="P59" t="inlineStr"/>
+      <c r="Q59" t="inlineStr"/>
+      <c r="R59" t="inlineStr"/>
+      <c r="S59" t="inlineStr"/>
+      <c r="T59" t="inlineStr"/>
+      <c r="U59" t="inlineStr"/>
+      <c r="V59" t="inlineStr"/>
+      <c r="W59" t="inlineStr"/>
+      <c r="X59" t="inlineStr"/>
+      <c r="Y59" t="inlineStr"/>
+      <c r="Z59" t="inlineStr"/>
+      <c r="AA59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>58</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>组成部门</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>1</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>审计署</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>主管国家财政收支审计监督，发布审计结果与整改信息。</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr"/>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>政务,审计,审计监督</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>访问官网 - www.audit.gov.cn</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>https://www.audit.gov.cn</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr"/>
+      <c r="N60" t="inlineStr"/>
+      <c r="O60" t="inlineStr"/>
+      <c r="P60" t="inlineStr"/>
+      <c r="Q60" t="inlineStr"/>
+      <c r="R60" t="inlineStr"/>
+      <c r="S60" t="inlineStr"/>
+      <c r="T60" t="inlineStr"/>
+      <c r="U60" t="inlineStr"/>
+      <c r="V60" t="inlineStr"/>
+      <c r="W60" t="inlineStr"/>
+      <c r="X60" t="inlineStr"/>
+      <c r="Y60" t="inlineStr"/>
+      <c r="Z60" t="inlineStr"/>
+      <c r="AA60" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/directory/gov/assets/xlsx/self_links.xlsx
+++ b/directory/gov/assets/xlsx/self_links.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="links" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,143 +413,408 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA60"/>
+  <dimension ref="A1:CB60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>站序</t>
+          <t>row_seq</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>分类</t>
+          <t>cat_id</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>type</t>
+          <t>cat_name</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>title</t>
+          <t>card_layout</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>desc</t>
+          <t>card_title</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>media</t>
+          <t>card_desc</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>tags</t>
+          <t>card_media</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>link1_name</t>
+          <t>card_tags</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>link1_url</t>
+          <t>card_id</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>link2_name</t>
+          <t>card_order</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>link2_url</t>
+          <t>link_1_id</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>link3_name</t>
+          <t>link_1_name</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>link3_url</t>
+          <t>link_1_url</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>link4_name</t>
+          <t>link_1_desc</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>link4_url</t>
+          <t>link_1_media</t>
         </is>
       </c>
       <c r="P1" t="inlineStr">
         <is>
-          <t>link5_name</t>
+          <t>link_1_enabled</t>
         </is>
       </c>
       <c r="Q1" t="inlineStr">
         <is>
-          <t>link5_url</t>
+          <t>link_2_id</t>
         </is>
       </c>
       <c r="R1" t="inlineStr">
         <is>
-          <t>link6_name</t>
+          <t>link_2_name</t>
         </is>
       </c>
       <c r="S1" t="inlineStr">
         <is>
-          <t>link6_url</t>
+          <t>link_2_url</t>
         </is>
       </c>
       <c r="T1" t="inlineStr">
         <is>
-          <t>link7_name</t>
+          <t>link_2_desc</t>
         </is>
       </c>
       <c r="U1" t="inlineStr">
         <is>
-          <t>link7_url</t>
+          <t>link_2_media</t>
         </is>
       </c>
       <c r="V1" t="inlineStr">
         <is>
-          <t>link8_name</t>
+          <t>link_2_enabled</t>
         </is>
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>link8_url</t>
+          <t>link_3_id</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>link9_name</t>
+          <t>link_3_name</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
         <is>
-          <t>link9_url</t>
+          <t>link_3_url</t>
         </is>
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>link10_name</t>
+          <t>link_3_desc</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
         <is>
-          <t>link10_url</t>
+          <t>link_3_media</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>link_3_enabled</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>link_4_id</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>link_4_name</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>link_4_url</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>link_4_desc</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>link_4_media</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>link_4_enabled</t>
+        </is>
+      </c>
+      <c r="AI1" t="inlineStr">
+        <is>
+          <t>link_5_id</t>
+        </is>
+      </c>
+      <c r="AJ1" t="inlineStr">
+        <is>
+          <t>link_5_name</t>
+        </is>
+      </c>
+      <c r="AK1" t="inlineStr">
+        <is>
+          <t>link_5_url</t>
+        </is>
+      </c>
+      <c r="AL1" t="inlineStr">
+        <is>
+          <t>link_5_desc</t>
+        </is>
+      </c>
+      <c r="AM1" t="inlineStr">
+        <is>
+          <t>link_5_media</t>
+        </is>
+      </c>
+      <c r="AN1" t="inlineStr">
+        <is>
+          <t>link_5_enabled</t>
+        </is>
+      </c>
+      <c r="AO1" t="inlineStr">
+        <is>
+          <t>link_6_id</t>
+        </is>
+      </c>
+      <c r="AP1" t="inlineStr">
+        <is>
+          <t>link_6_name</t>
+        </is>
+      </c>
+      <c r="AQ1" t="inlineStr">
+        <is>
+          <t>link_6_url</t>
+        </is>
+      </c>
+      <c r="AR1" t="inlineStr">
+        <is>
+          <t>link_6_desc</t>
+        </is>
+      </c>
+      <c r="AS1" t="inlineStr">
+        <is>
+          <t>link_6_media</t>
+        </is>
+      </c>
+      <c r="AT1" t="inlineStr">
+        <is>
+          <t>link_6_enabled</t>
+        </is>
+      </c>
+      <c r="AU1" t="inlineStr">
+        <is>
+          <t>link_7_id</t>
+        </is>
+      </c>
+      <c r="AV1" t="inlineStr">
+        <is>
+          <t>link_7_name</t>
+        </is>
+      </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>link_7_url</t>
+        </is>
+      </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>link_7_desc</t>
+        </is>
+      </c>
+      <c r="AY1" t="inlineStr">
+        <is>
+          <t>link_7_media</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>link_7_enabled</t>
+        </is>
+      </c>
+      <c r="BA1" t="inlineStr">
+        <is>
+          <t>link_8_id</t>
+        </is>
+      </c>
+      <c r="BB1" t="inlineStr">
+        <is>
+          <t>link_8_name</t>
+        </is>
+      </c>
+      <c r="BC1" t="inlineStr">
+        <is>
+          <t>link_8_url</t>
+        </is>
+      </c>
+      <c r="BD1" t="inlineStr">
+        <is>
+          <t>link_8_desc</t>
+        </is>
+      </c>
+      <c r="BE1" t="inlineStr">
+        <is>
+          <t>link_8_media</t>
+        </is>
+      </c>
+      <c r="BF1" t="inlineStr">
+        <is>
+          <t>link_8_enabled</t>
+        </is>
+      </c>
+      <c r="BG1" t="inlineStr">
+        <is>
+          <t>link_9_id</t>
+        </is>
+      </c>
+      <c r="BH1" t="inlineStr">
+        <is>
+          <t>link_9_name</t>
+        </is>
+      </c>
+      <c r="BI1" t="inlineStr">
+        <is>
+          <t>link_9_url</t>
+        </is>
+      </c>
+      <c r="BJ1" t="inlineStr">
+        <is>
+          <t>link_9_desc</t>
+        </is>
+      </c>
+      <c r="BK1" t="inlineStr">
+        <is>
+          <t>link_9_media</t>
+        </is>
+      </c>
+      <c r="BL1" t="inlineStr">
+        <is>
+          <t>link_9_enabled</t>
+        </is>
+      </c>
+      <c r="BM1" t="inlineStr">
+        <is>
+          <t>link_10_id</t>
+        </is>
+      </c>
+      <c r="BN1" t="inlineStr">
+        <is>
+          <t>link_10_name</t>
+        </is>
+      </c>
+      <c r="BO1" t="inlineStr">
+        <is>
+          <t>link_10_url</t>
+        </is>
+      </c>
+      <c r="BP1" t="inlineStr">
+        <is>
+          <t>link_10_desc</t>
+        </is>
+      </c>
+      <c r="BQ1" t="inlineStr">
+        <is>
+          <t>link_10_media</t>
+        </is>
+      </c>
+      <c r="BR1" t="inlineStr">
+        <is>
+          <t>link_10_enabled</t>
+        </is>
+      </c>
+      <c r="BS1" t="inlineStr">
+        <is>
+          <t>source_1_name</t>
+        </is>
+      </c>
+      <c r="BT1" t="inlineStr">
+        <is>
+          <t>source_1_url</t>
+        </is>
+      </c>
+      <c r="BU1" t="inlineStr">
+        <is>
+          <t>source_2_name</t>
+        </is>
+      </c>
+      <c r="BV1" t="inlineStr">
+        <is>
+          <t>source_2_url</t>
+        </is>
+      </c>
+      <c r="BW1" t="inlineStr">
+        <is>
+          <t>source_3_name</t>
+        </is>
+      </c>
+      <c r="BX1" t="inlineStr">
+        <is>
+          <t>source_3_url</t>
+        </is>
+      </c>
+      <c r="BY1" t="inlineStr">
+        <is>
+          <t>source_4_name</t>
+        </is>
+      </c>
+      <c r="BZ1" t="inlineStr">
+        <is>
+          <t>source_4_url</t>
+        </is>
+      </c>
+      <c r="CA1" t="inlineStr">
+        <is>
+          <t>source_5_name</t>
+        </is>
+      </c>
+      <c r="CB1" t="inlineStr">
+        <is>
+          <t>source_5_url</t>
         </is>
       </c>
     </row>
@@ -557,3364 +822,2283 @@
       <c r="A2" t="n">
         <v>0</v>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>全国</t>
         </is>
       </c>
-      <c r="C2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2" t="inlineStr">
         <is>
           <t>全国人民代表大会</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>最高国家权力机关，行使国家立法权，官方网站发布法律、公报与常委会信息。</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>人大,全国人大,国家立法</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>访问官网 - www.npc.gov.cn</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>https://www.npc.gov.cn</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr"/>
-      <c r="S2" t="inlineStr"/>
-      <c r="T2" t="inlineStr"/>
-      <c r="U2" t="inlineStr"/>
-      <c r="V2" t="inlineStr"/>
-      <c r="W2" t="inlineStr"/>
-      <c r="X2" t="inlineStr"/>
-      <c r="Y2" t="inlineStr"/>
-      <c r="Z2" t="inlineStr"/>
-      <c r="AA2" t="inlineStr"/>
+      <c r="BS2" t="inlineStr">
+        <is>
+          <t>百度百科</t>
+        </is>
+      </c>
+      <c r="BT2" t="inlineStr">
+        <is>
+          <t>https://baike.baidu.com/item/%E5%85%A8%E5%9B%BD%E4%BA%BA%E6%B0%91%E4%BB%A3%E8%A1%A8%E5%A4%A7%E4%BC%9A</t>
+        </is>
+      </c>
+      <c r="BU2" t="inlineStr">
+        <is>
+          <t>中国政府网</t>
+        </is>
+      </c>
+      <c r="BV2" t="inlineStr">
+        <is>
+          <t>https://www.gov.cn</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
         <v>1</v>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>直辖市</t>
         </is>
       </c>
-      <c r="C3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D3" t="inlineStr">
+      <c r="D3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" t="inlineStr">
         <is>
           <t>北京市人民代表大会常务委员会</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>北京市人民代表大会常设机关，发布地方立法、监督与代表工作信息。</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>人大,北京,直辖市</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>访问官网 - www.bjrd.gov.cn</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>https://www.bjrd.gov.cn</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr"/>
-      <c r="R3" t="inlineStr"/>
-      <c r="S3" t="inlineStr"/>
-      <c r="T3" t="inlineStr"/>
-      <c r="U3" t="inlineStr"/>
-      <c r="V3" t="inlineStr"/>
-      <c r="W3" t="inlineStr"/>
-      <c r="X3" t="inlineStr"/>
-      <c r="Y3" t="inlineStr"/>
-      <c r="Z3" t="inlineStr"/>
-      <c r="AA3" t="inlineStr"/>
+      <c r="BS3" t="inlineStr">
+        <is>
+          <t>百度百科</t>
+        </is>
+      </c>
+      <c r="BT3" t="inlineStr">
+        <is>
+          <t>https://baike.baidu.com/item/%E5%8C%97%E4%BA%AC%E5%B8%82%E4%BA%BA%E6%B0%91%E4%BB%A3%E8%A1%A8%E5%A4%A7%E4%BC%9A%E5%B8%B8%E5%8A%A1%E5%A7%94%E5%91%98%E4%BC%9A</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
         <v>2</v>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>直辖市</t>
         </is>
       </c>
-      <c r="C4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D4" t="inlineStr">
+      <c r="D4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" t="inlineStr">
         <is>
           <t>上海市人民代表大会常务委员会</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>上海市人民代表大会常设机关，地方立法与监督工作平台。</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>人大,上海,直辖市</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>访问官网 - www.shrd.gov.cn</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>https://www.shrd.gov.cn</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr"/>
-      <c r="R4" t="inlineStr"/>
-      <c r="S4" t="inlineStr"/>
-      <c r="T4" t="inlineStr"/>
-      <c r="U4" t="inlineStr"/>
-      <c r="V4" t="inlineStr"/>
-      <c r="W4" t="inlineStr"/>
-      <c r="X4" t="inlineStr"/>
-      <c r="Y4" t="inlineStr"/>
-      <c r="Z4" t="inlineStr"/>
-      <c r="AA4" t="inlineStr"/>
+      <c r="BS4" t="inlineStr">
+        <is>
+          <t>百度百科</t>
+        </is>
+      </c>
+      <c r="BT4" t="inlineStr">
+        <is>
+          <t>https://baike.baidu.com/item/%E4%B8%8A%E6%B5%B7%E5%B8%82%E4%BA%BA%E6%B0%91%E4%BB%A3%E8%A1%A8%E5%A4%A7%E4%BC%9A%E5%B8%B8%E5%8A%A1%E5%A7%94%E5%91%98%E4%BC%9A</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
         <v>3</v>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>直辖市</t>
         </is>
       </c>
-      <c r="C5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D5" t="inlineStr">
+      <c r="D5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" t="inlineStr">
         <is>
           <t>天津市人民代表大会常务委员会</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>天津市人民代表大会常设机关，发布地方性法规与监督信息。</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>人大,天津,直辖市</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>访问官网 - www.tjrd.gov.cn</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>https://www.tjrd.gov.cn</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr"/>
-      <c r="R5" t="inlineStr"/>
-      <c r="S5" t="inlineStr"/>
-      <c r="T5" t="inlineStr"/>
-      <c r="U5" t="inlineStr"/>
-      <c r="V5" t="inlineStr"/>
-      <c r="W5" t="inlineStr"/>
-      <c r="X5" t="inlineStr"/>
-      <c r="Y5" t="inlineStr"/>
-      <c r="Z5" t="inlineStr"/>
-      <c r="AA5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
         <v>4</v>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>直辖市</t>
         </is>
       </c>
-      <c r="C6" t="n">
-        <v>1</v>
-      </c>
-      <c r="D6" t="inlineStr">
+      <c r="D6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" t="inlineStr">
         <is>
           <t>重庆市人民代表大会常务委员会</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>重庆市人民代表大会常设机关，地方立法与代表工作平台。</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>人大,重庆,直辖市</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>访问官网 - www.cqrd.gov.cn</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>https://www.cqrd.gov.cn</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr"/>
-      <c r="R6" t="inlineStr"/>
-      <c r="S6" t="inlineStr"/>
-      <c r="T6" t="inlineStr"/>
-      <c r="U6" t="inlineStr"/>
-      <c r="V6" t="inlineStr"/>
-      <c r="W6" t="inlineStr"/>
-      <c r="X6" t="inlineStr"/>
-      <c r="Y6" t="inlineStr"/>
-      <c r="Z6" t="inlineStr"/>
-      <c r="AA6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
         <v>5</v>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>省</t>
         </is>
       </c>
-      <c r="C7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D7" t="inlineStr">
+      <c r="D7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" t="inlineStr">
         <is>
           <t>河北省人民代表大会常务委员会</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>河北省人民代表大会常设机关，发布地方立法、监督与代表履职信息。</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>人大,河北,省</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>访问官网 - www.hbrd.gov.cn</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>https://www.hbrd.gov.cn</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr"/>
-      <c r="R7" t="inlineStr"/>
-      <c r="S7" t="inlineStr"/>
-      <c r="T7" t="inlineStr"/>
-      <c r="U7" t="inlineStr"/>
-      <c r="V7" t="inlineStr"/>
-      <c r="W7" t="inlineStr"/>
-      <c r="X7" t="inlineStr"/>
-      <c r="Y7" t="inlineStr"/>
-      <c r="Z7" t="inlineStr"/>
-      <c r="AA7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
         <v>6</v>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>省</t>
         </is>
       </c>
-      <c r="C8" t="n">
-        <v>1</v>
-      </c>
-      <c r="D8" t="inlineStr">
+      <c r="D8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E8" t="inlineStr">
         <is>
           <t>山西省人民代表大会常务委员会</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>山西省人民代表大会常设机关，发布地方性法规与监督工作信息。</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>人大,山西,省</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>访问官网 - www.sxpc.gov.cn</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>https://www.sxpc.gov.cn</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="inlineStr"/>
-      <c r="R8" t="inlineStr"/>
-      <c r="S8" t="inlineStr"/>
-      <c r="T8" t="inlineStr"/>
-      <c r="U8" t="inlineStr"/>
-      <c r="V8" t="inlineStr"/>
-      <c r="W8" t="inlineStr"/>
-      <c r="X8" t="inlineStr"/>
-      <c r="Y8" t="inlineStr"/>
-      <c r="Z8" t="inlineStr"/>
-      <c r="AA8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
         <v>7</v>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>省</t>
         </is>
       </c>
-      <c r="C9" t="n">
-        <v>1</v>
-      </c>
-      <c r="D9" t="inlineStr">
+      <c r="D9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" t="inlineStr">
         <is>
           <t>辽宁省人民代表大会常务委员会</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>辽宁省人民代表大会常设机关，发布地方立法与代表工作信息。</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>人大,辽宁,省</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>访问官网 - www.lnrd.gov.cn</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>https://www.lnrd.gov.cn</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr"/>
-      <c r="Q9" t="inlineStr"/>
-      <c r="R9" t="inlineStr"/>
-      <c r="S9" t="inlineStr"/>
-      <c r="T9" t="inlineStr"/>
-      <c r="U9" t="inlineStr"/>
-      <c r="V9" t="inlineStr"/>
-      <c r="W9" t="inlineStr"/>
-      <c r="X9" t="inlineStr"/>
-      <c r="Y9" t="inlineStr"/>
-      <c r="Z9" t="inlineStr"/>
-      <c r="AA9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
         <v>8</v>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>省</t>
         </is>
       </c>
-      <c r="C10" t="n">
-        <v>1</v>
-      </c>
-      <c r="D10" t="inlineStr">
+      <c r="D10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" t="inlineStr">
         <is>
           <t>吉林省人民代表大会常务委员会</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>吉林省人民代表大会常设机关，发布地方性法规与监督信息。</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>人大,吉林,省</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>访问官网 - www.jlrd.gov.cn</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>https://www.jlrd.gov.cn</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr"/>
-      <c r="P10" t="inlineStr"/>
-      <c r="Q10" t="inlineStr"/>
-      <c r="R10" t="inlineStr"/>
-      <c r="S10" t="inlineStr"/>
-      <c r="T10" t="inlineStr"/>
-      <c r="U10" t="inlineStr"/>
-      <c r="V10" t="inlineStr"/>
-      <c r="W10" t="inlineStr"/>
-      <c r="X10" t="inlineStr"/>
-      <c r="Y10" t="inlineStr"/>
-      <c r="Z10" t="inlineStr"/>
-      <c r="AA10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
         <v>9</v>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>省</t>
         </is>
       </c>
-      <c r="C11" t="n">
-        <v>1</v>
-      </c>
-      <c r="D11" t="inlineStr">
+      <c r="D11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E11" t="inlineStr">
         <is>
           <t>黑龙江省人民代表大会常务委员会</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>黑龙江省人民代表大会常设机关，发布地方立法、监督与代表工作信息。</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>人大,黑龙江,省</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t>访问官网 - www.hljrd.gov.cn</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>https://www.hljrd.gov.cn</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr"/>
-      <c r="P11" t="inlineStr"/>
-      <c r="Q11" t="inlineStr"/>
-      <c r="R11" t="inlineStr"/>
-      <c r="S11" t="inlineStr"/>
-      <c r="T11" t="inlineStr"/>
-      <c r="U11" t="inlineStr"/>
-      <c r="V11" t="inlineStr"/>
-      <c r="W11" t="inlineStr"/>
-      <c r="X11" t="inlineStr"/>
-      <c r="Y11" t="inlineStr"/>
-      <c r="Z11" t="inlineStr"/>
-      <c r="AA11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
         <v>10</v>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>省</t>
         </is>
       </c>
-      <c r="C12" t="n">
-        <v>1</v>
-      </c>
-      <c r="D12" t="inlineStr">
+      <c r="D12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E12" t="inlineStr">
         <is>
           <t>江苏省人民代表大会常务委员会</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>江苏省人民代表大会常设机关，地方立法与监督工作平台。</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>人大,江苏,省</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t>访问官网 - www.jsrd.gov.cn</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>https://www.jsrd.gov.cn</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
-      <c r="O12" t="inlineStr"/>
-      <c r="P12" t="inlineStr"/>
-      <c r="Q12" t="inlineStr"/>
-      <c r="R12" t="inlineStr"/>
-      <c r="S12" t="inlineStr"/>
-      <c r="T12" t="inlineStr"/>
-      <c r="U12" t="inlineStr"/>
-      <c r="V12" t="inlineStr"/>
-      <c r="W12" t="inlineStr"/>
-      <c r="X12" t="inlineStr"/>
-      <c r="Y12" t="inlineStr"/>
-      <c r="Z12" t="inlineStr"/>
-      <c r="AA12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
         <v>11</v>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>省</t>
         </is>
       </c>
-      <c r="C13" t="n">
-        <v>1</v>
-      </c>
-      <c r="D13" t="inlineStr">
+      <c r="D13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E13" t="inlineStr">
         <is>
           <t>浙江省人民代表大会常务委员会</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>浙江省人民代表大会常设机关，发布地方性法规与代表信息。</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>人大,浙江,省</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="L13" t="inlineStr">
         <is>
           <t>访问官网 - www.zjrd.gov.cn</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t>https://www.zjrd.gov.cn</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
-      <c r="O13" t="inlineStr"/>
-      <c r="P13" t="inlineStr"/>
-      <c r="Q13" t="inlineStr"/>
-      <c r="R13" t="inlineStr"/>
-      <c r="S13" t="inlineStr"/>
-      <c r="T13" t="inlineStr"/>
-      <c r="U13" t="inlineStr"/>
-      <c r="V13" t="inlineStr"/>
-      <c r="W13" t="inlineStr"/>
-      <c r="X13" t="inlineStr"/>
-      <c r="Y13" t="inlineStr"/>
-      <c r="Z13" t="inlineStr"/>
-      <c r="AA13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
         <v>12</v>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>省</t>
         </is>
       </c>
-      <c r="C14" t="n">
-        <v>1</v>
-      </c>
-      <c r="D14" t="inlineStr">
+      <c r="D14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E14" t="inlineStr">
         <is>
           <t>安徽省人民代表大会常务委员会</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>安徽省人民代表大会常设机关，发布地方立法与代表履职信息。</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr">
+      <c r="H14" t="inlineStr">
         <is>
           <t>人大,安徽,省</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="L14" t="inlineStr">
         <is>
           <t>访问官网 - www.ahrd.gov.cn</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
+      <c r="M14" t="inlineStr">
         <is>
           <t>https://www.ahrd.gov.cn</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr"/>
-      <c r="P14" t="inlineStr"/>
-      <c r="Q14" t="inlineStr"/>
-      <c r="R14" t="inlineStr"/>
-      <c r="S14" t="inlineStr"/>
-      <c r="T14" t="inlineStr"/>
-      <c r="U14" t="inlineStr"/>
-      <c r="V14" t="inlineStr"/>
-      <c r="W14" t="inlineStr"/>
-      <c r="X14" t="inlineStr"/>
-      <c r="Y14" t="inlineStr"/>
-      <c r="Z14" t="inlineStr"/>
-      <c r="AA14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
         <v>13</v>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>省</t>
         </is>
       </c>
-      <c r="C15" t="n">
-        <v>1</v>
-      </c>
-      <c r="D15" t="inlineStr">
+      <c r="D15" t="n">
+        <v>1</v>
+      </c>
+      <c r="E15" t="inlineStr">
         <is>
           <t>福建省人民代表大会常务委员会</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>福建省人民代表大会常设机关，发布地方性法规与监督工作信息。</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr">
+      <c r="H15" t="inlineStr">
         <is>
           <t>人大,福建,省</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="L15" t="inlineStr">
         <is>
           <t>访问官网 - www.fjrd.gov.cn</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
+      <c r="M15" t="inlineStr">
         <is>
           <t>https://www.fjrd.gov.cn</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
-      <c r="O15" t="inlineStr"/>
-      <c r="P15" t="inlineStr"/>
-      <c r="Q15" t="inlineStr"/>
-      <c r="R15" t="inlineStr"/>
-      <c r="S15" t="inlineStr"/>
-      <c r="T15" t="inlineStr"/>
-      <c r="U15" t="inlineStr"/>
-      <c r="V15" t="inlineStr"/>
-      <c r="W15" t="inlineStr"/>
-      <c r="X15" t="inlineStr"/>
-      <c r="Y15" t="inlineStr"/>
-      <c r="Z15" t="inlineStr"/>
-      <c r="AA15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
         <v>14</v>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>省</t>
         </is>
       </c>
-      <c r="C16" t="n">
-        <v>1</v>
-      </c>
-      <c r="D16" t="inlineStr">
+      <c r="D16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E16" t="inlineStr">
         <is>
           <t>江西省人民代表大会常务委员会</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>江西省人民代表大会常设机关，发布地方立法与代表工作信息。</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr">
+      <c r="H16" t="inlineStr">
         <is>
           <t>人大,江西,省</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="L16" t="inlineStr">
         <is>
           <t>访问官网 - www.jxrd.gov.cn</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
+      <c r="M16" t="inlineStr">
         <is>
           <t>https://www.jxrd.gov.cn</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
-      <c r="O16" t="inlineStr"/>
-      <c r="P16" t="inlineStr"/>
-      <c r="Q16" t="inlineStr"/>
-      <c r="R16" t="inlineStr"/>
-      <c r="S16" t="inlineStr"/>
-      <c r="T16" t="inlineStr"/>
-      <c r="U16" t="inlineStr"/>
-      <c r="V16" t="inlineStr"/>
-      <c r="W16" t="inlineStr"/>
-      <c r="X16" t="inlineStr"/>
-      <c r="Y16" t="inlineStr"/>
-      <c r="Z16" t="inlineStr"/>
-      <c r="AA16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
         <v>15</v>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>省</t>
         </is>
       </c>
-      <c r="C17" t="n">
-        <v>1</v>
-      </c>
-      <c r="D17" t="inlineStr">
+      <c r="D17" t="n">
+        <v>1</v>
+      </c>
+      <c r="E17" t="inlineStr">
         <is>
           <t>山东省人民代表大会常务委员会</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>山东省人民代表大会常设机关，地方立法与监督工作平台。</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr">
+      <c r="H17" t="inlineStr">
         <is>
           <t>人大,山东,省</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="L17" t="inlineStr">
         <is>
           <t>访问官网 - www.sdrd.gov.cn</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
+      <c r="M17" t="inlineStr">
         <is>
           <t>https://www.sdrd.gov.cn</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
-      <c r="O17" t="inlineStr"/>
-      <c r="P17" t="inlineStr"/>
-      <c r="Q17" t="inlineStr"/>
-      <c r="R17" t="inlineStr"/>
-      <c r="S17" t="inlineStr"/>
-      <c r="T17" t="inlineStr"/>
-      <c r="U17" t="inlineStr"/>
-      <c r="V17" t="inlineStr"/>
-      <c r="W17" t="inlineStr"/>
-      <c r="X17" t="inlineStr"/>
-      <c r="Y17" t="inlineStr"/>
-      <c r="Z17" t="inlineStr"/>
-      <c r="AA17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
         <v>16</v>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>省</t>
         </is>
       </c>
-      <c r="C18" t="n">
-        <v>1</v>
-      </c>
-      <c r="D18" t="inlineStr">
+      <c r="D18" t="n">
+        <v>1</v>
+      </c>
+      <c r="E18" t="inlineStr">
         <is>
           <t>河南省人民代表大会常务委员会</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>河南省人民代表大会常设机关，发布地方性法规与监督信息。</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr">
+      <c r="H18" t="inlineStr">
         <is>
           <t>人大,河南,省</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="L18" t="inlineStr">
         <is>
           <t>访问官网 - www.henanrd.gov.cn</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
+      <c r="M18" t="inlineStr">
         <is>
           <t>https://www.henanrd.gov.cn</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
-      <c r="O18" t="inlineStr"/>
-      <c r="P18" t="inlineStr"/>
-      <c r="Q18" t="inlineStr"/>
-      <c r="R18" t="inlineStr"/>
-      <c r="S18" t="inlineStr"/>
-      <c r="T18" t="inlineStr"/>
-      <c r="U18" t="inlineStr"/>
-      <c r="V18" t="inlineStr"/>
-      <c r="W18" t="inlineStr"/>
-      <c r="X18" t="inlineStr"/>
-      <c r="Y18" t="inlineStr"/>
-      <c r="Z18" t="inlineStr"/>
-      <c r="AA18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
         <v>17</v>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>省</t>
         </is>
       </c>
-      <c r="C19" t="n">
-        <v>1</v>
-      </c>
-      <c r="D19" t="inlineStr">
+      <c r="D19" t="n">
+        <v>1</v>
+      </c>
+      <c r="E19" t="inlineStr">
         <is>
           <t>湖北省人民代表大会常务委员会</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="F19" t="inlineStr">
         <is>
           <t>湖北省人民代表大会常设机关，地方立法与代表工作平台。</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr">
+      <c r="H19" t="inlineStr">
         <is>
           <t>人大,湖北,省</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
+      <c r="L19" t="inlineStr">
         <is>
           <t>访问官网 - www.hppc.gov.cn</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
+      <c r="M19" t="inlineStr">
         <is>
           <t>https://www.hppc.gov.cn</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
-      <c r="O19" t="inlineStr"/>
-      <c r="P19" t="inlineStr"/>
-      <c r="Q19" t="inlineStr"/>
-      <c r="R19" t="inlineStr"/>
-      <c r="S19" t="inlineStr"/>
-      <c r="T19" t="inlineStr"/>
-      <c r="U19" t="inlineStr"/>
-      <c r="V19" t="inlineStr"/>
-      <c r="W19" t="inlineStr"/>
-      <c r="X19" t="inlineStr"/>
-      <c r="Y19" t="inlineStr"/>
-      <c r="Z19" t="inlineStr"/>
-      <c r="AA19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
         <v>18</v>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>省</t>
         </is>
       </c>
-      <c r="C20" t="n">
-        <v>1</v>
-      </c>
-      <c r="D20" t="inlineStr">
+      <c r="D20" t="n">
+        <v>1</v>
+      </c>
+      <c r="E20" t="inlineStr">
         <is>
           <t>湖南省人民代表大会常务委员会</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="F20" t="inlineStr">
         <is>
           <t>湖南省人民代表大会常设机关，发布地方性法规与监督信息。</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr">
+      <c r="H20" t="inlineStr">
         <is>
           <t>人大,湖南,省</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
+      <c r="L20" t="inlineStr">
         <is>
           <t>访问官网 - www.hnrd.gov.cn</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
+      <c r="M20" t="inlineStr">
         <is>
           <t>https://www.hnrd.gov.cn</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
-      <c r="O20" t="inlineStr"/>
-      <c r="P20" t="inlineStr"/>
-      <c r="Q20" t="inlineStr"/>
-      <c r="R20" t="inlineStr"/>
-      <c r="S20" t="inlineStr"/>
-      <c r="T20" t="inlineStr"/>
-      <c r="U20" t="inlineStr"/>
-      <c r="V20" t="inlineStr"/>
-      <c r="W20" t="inlineStr"/>
-      <c r="X20" t="inlineStr"/>
-      <c r="Y20" t="inlineStr"/>
-      <c r="Z20" t="inlineStr"/>
-      <c r="AA20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
         <v>19</v>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>省</t>
         </is>
       </c>
-      <c r="C21" t="n">
-        <v>1</v>
-      </c>
-      <c r="D21" t="inlineStr">
+      <c r="D21" t="n">
+        <v>1</v>
+      </c>
+      <c r="E21" t="inlineStr">
         <is>
           <t>广东省人民代表大会常务委员会</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="F21" t="inlineStr">
         <is>
           <t>广东省人民代表大会常设机关，发布地方性法规与监督信息。</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr">
+      <c r="H21" t="inlineStr">
         <is>
           <t>人大,广东,省</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
+      <c r="L21" t="inlineStr">
         <is>
           <t>访问官网 - www.rd.gd.cn</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
+      <c r="M21" t="inlineStr">
         <is>
           <t>https://www.rd.gd.cn</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
-      <c r="O21" t="inlineStr"/>
-      <c r="P21" t="inlineStr"/>
-      <c r="Q21" t="inlineStr"/>
-      <c r="R21" t="inlineStr"/>
-      <c r="S21" t="inlineStr"/>
-      <c r="T21" t="inlineStr"/>
-      <c r="U21" t="inlineStr"/>
-      <c r="V21" t="inlineStr"/>
-      <c r="W21" t="inlineStr"/>
-      <c r="X21" t="inlineStr"/>
-      <c r="Y21" t="inlineStr"/>
-      <c r="Z21" t="inlineStr"/>
-      <c r="AA21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
         <v>20</v>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="C22" t="inlineStr">
         <is>
           <t>省</t>
         </is>
       </c>
-      <c r="C22" t="n">
-        <v>1</v>
-      </c>
-      <c r="D22" t="inlineStr">
+      <c r="D22" t="n">
+        <v>1</v>
+      </c>
+      <c r="E22" t="inlineStr">
         <is>
           <t>海南省人民代表大会常务委员会</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="F22" t="inlineStr">
         <is>
           <t>海南省人民代表大会常设机关，发布地方立法、监督与代表工作信息。</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr">
+      <c r="H22" t="inlineStr">
         <is>
           <t>人大,海南,省</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
+      <c r="L22" t="inlineStr">
         <is>
           <t>访问官网 - www.hainanpc.gov.cn</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
+      <c r="M22" t="inlineStr">
         <is>
           <t>https://www.hainanpc.gov.cn</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
-      <c r="O22" t="inlineStr"/>
-      <c r="P22" t="inlineStr"/>
-      <c r="Q22" t="inlineStr"/>
-      <c r="R22" t="inlineStr"/>
-      <c r="S22" t="inlineStr"/>
-      <c r="T22" t="inlineStr"/>
-      <c r="U22" t="inlineStr"/>
-      <c r="V22" t="inlineStr"/>
-      <c r="W22" t="inlineStr"/>
-      <c r="X22" t="inlineStr"/>
-      <c r="Y22" t="inlineStr"/>
-      <c r="Z22" t="inlineStr"/>
-      <c r="AA22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
         <v>21</v>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="C23" t="inlineStr">
         <is>
           <t>省</t>
         </is>
       </c>
-      <c r="C23" t="n">
-        <v>1</v>
-      </c>
-      <c r="D23" t="inlineStr">
+      <c r="D23" t="n">
+        <v>1</v>
+      </c>
+      <c r="E23" t="inlineStr">
         <is>
           <t>四川省人民代表大会常务委员会</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="F23" t="inlineStr">
         <is>
           <t>四川省人民代表大会常设机关，发布地方性法规与监督信息。</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr">
+      <c r="H23" t="inlineStr">
         <is>
           <t>人大,四川,省</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
+      <c r="L23" t="inlineStr">
         <is>
           <t>访问官网 - www.scspc.gov.cn</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
+      <c r="M23" t="inlineStr">
         <is>
           <t>https://www.scspc.gov.cn</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
-      <c r="O23" t="inlineStr"/>
-      <c r="P23" t="inlineStr"/>
-      <c r="Q23" t="inlineStr"/>
-      <c r="R23" t="inlineStr"/>
-      <c r="S23" t="inlineStr"/>
-      <c r="T23" t="inlineStr"/>
-      <c r="U23" t="inlineStr"/>
-      <c r="V23" t="inlineStr"/>
-      <c r="W23" t="inlineStr"/>
-      <c r="X23" t="inlineStr"/>
-      <c r="Y23" t="inlineStr"/>
-      <c r="Z23" t="inlineStr"/>
-      <c r="AA23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
         <v>22</v>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="C24" t="inlineStr">
         <is>
           <t>省</t>
         </is>
       </c>
-      <c r="C24" t="n">
-        <v>1</v>
-      </c>
-      <c r="D24" t="inlineStr">
+      <c r="D24" t="n">
+        <v>1</v>
+      </c>
+      <c r="E24" t="inlineStr">
         <is>
           <t>贵州省人民代表大会常务委员会</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="F24" t="inlineStr">
         <is>
           <t>贵州省人民代表大会常设机关，发布地方性法规与监督信息。</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr">
+      <c r="H24" t="inlineStr">
         <is>
           <t>人大,贵州,省</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
+      <c r="L24" t="inlineStr">
         <is>
           <t>访问官网 - www.gzrd.gov.cn</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
+      <c r="M24" t="inlineStr">
         <is>
           <t>https://www.gzrd.gov.cn</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
-      <c r="O24" t="inlineStr"/>
-      <c r="P24" t="inlineStr"/>
-      <c r="Q24" t="inlineStr"/>
-      <c r="R24" t="inlineStr"/>
-      <c r="S24" t="inlineStr"/>
-      <c r="T24" t="inlineStr"/>
-      <c r="U24" t="inlineStr"/>
-      <c r="V24" t="inlineStr"/>
-      <c r="W24" t="inlineStr"/>
-      <c r="X24" t="inlineStr"/>
-      <c r="Y24" t="inlineStr"/>
-      <c r="Z24" t="inlineStr"/>
-      <c r="AA24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
         <v>23</v>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t>省</t>
         </is>
       </c>
-      <c r="C25" t="n">
-        <v>1</v>
-      </c>
-      <c r="D25" t="inlineStr">
+      <c r="D25" t="n">
+        <v>1</v>
+      </c>
+      <c r="E25" t="inlineStr">
         <is>
           <t>云南省人民代表大会常务委员会</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="F25" t="inlineStr">
         <is>
           <t>云南省人民代表大会常设机关，发布地方立法与代表履职信息。</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr">
+      <c r="H25" t="inlineStr">
         <is>
           <t>人大,云南,省</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
+      <c r="L25" t="inlineStr">
         <is>
           <t>访问官网 - www.ynrd.gov.cn</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
+      <c r="M25" t="inlineStr">
         <is>
           <t>https://www.ynrd.gov.cn</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
-      <c r="O25" t="inlineStr"/>
-      <c r="P25" t="inlineStr"/>
-      <c r="Q25" t="inlineStr"/>
-      <c r="R25" t="inlineStr"/>
-      <c r="S25" t="inlineStr"/>
-      <c r="T25" t="inlineStr"/>
-      <c r="U25" t="inlineStr"/>
-      <c r="V25" t="inlineStr"/>
-      <c r="W25" t="inlineStr"/>
-      <c r="X25" t="inlineStr"/>
-      <c r="Y25" t="inlineStr"/>
-      <c r="Z25" t="inlineStr"/>
-      <c r="AA25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
         <v>24</v>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="C26" t="inlineStr">
         <is>
           <t>省</t>
         </is>
       </c>
-      <c r="C26" t="n">
-        <v>1</v>
-      </c>
-      <c r="D26" t="inlineStr">
+      <c r="D26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E26" t="inlineStr">
         <is>
           <t>陕西省人民代表大会常务委员会</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="F26" t="inlineStr">
         <is>
           <t>陕西省人民代表大会常设机关，发布地方性法规与监督工作信息。</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr">
+      <c r="H26" t="inlineStr">
         <is>
           <t>人大,陕西,省</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
+      <c r="L26" t="inlineStr">
         <is>
           <t>访问官网 - www.sxrd.gov.cn</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
+      <c r="M26" t="inlineStr">
         <is>
           <t>https://www.sxrd.gov.cn</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
-      <c r="O26" t="inlineStr"/>
-      <c r="P26" t="inlineStr"/>
-      <c r="Q26" t="inlineStr"/>
-      <c r="R26" t="inlineStr"/>
-      <c r="S26" t="inlineStr"/>
-      <c r="T26" t="inlineStr"/>
-      <c r="U26" t="inlineStr"/>
-      <c r="V26" t="inlineStr"/>
-      <c r="W26" t="inlineStr"/>
-      <c r="X26" t="inlineStr"/>
-      <c r="Y26" t="inlineStr"/>
-      <c r="Z26" t="inlineStr"/>
-      <c r="AA26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
         <v>25</v>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="C27" t="inlineStr">
         <is>
           <t>省</t>
         </is>
       </c>
-      <c r="C27" t="n">
-        <v>1</v>
-      </c>
-      <c r="D27" t="inlineStr">
+      <c r="D27" t="n">
+        <v>1</v>
+      </c>
+      <c r="E27" t="inlineStr">
         <is>
           <t>甘肃省人民代表大会常务委员会</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="F27" t="inlineStr">
         <is>
           <t>甘肃省人民代表大会常设机关，发布地方立法与代表工作信息。</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr">
+      <c r="H27" t="inlineStr">
         <is>
           <t>人大,甘肃,省</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
+      <c r="L27" t="inlineStr">
         <is>
           <t>访问官网 - www.gsrdw.gov.cn</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
+      <c r="M27" t="inlineStr">
         <is>
           <t>https://www.gsrdw.gov.cn</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
-      <c r="O27" t="inlineStr"/>
-      <c r="P27" t="inlineStr"/>
-      <c r="Q27" t="inlineStr"/>
-      <c r="R27" t="inlineStr"/>
-      <c r="S27" t="inlineStr"/>
-      <c r="T27" t="inlineStr"/>
-      <c r="U27" t="inlineStr"/>
-      <c r="V27" t="inlineStr"/>
-      <c r="W27" t="inlineStr"/>
-      <c r="X27" t="inlineStr"/>
-      <c r="Y27" t="inlineStr"/>
-      <c r="Z27" t="inlineStr"/>
-      <c r="AA27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
         <v>26</v>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="C28" t="inlineStr">
         <is>
           <t>省</t>
         </is>
       </c>
-      <c r="C28" t="n">
-        <v>1</v>
-      </c>
-      <c r="D28" t="inlineStr">
+      <c r="D28" t="n">
+        <v>1</v>
+      </c>
+      <c r="E28" t="inlineStr">
         <is>
           <t>青海省人民代表大会常务委员会</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="F28" t="inlineStr">
         <is>
           <t>青海省人民代表大会常设机关，发布地方性法规与监督信息。</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr">
+      <c r="H28" t="inlineStr">
         <is>
           <t>人大,青海,省</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
+      <c r="L28" t="inlineStr">
         <is>
           <t>访问官网 - www.qhrd.gov.cn</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
+      <c r="M28" t="inlineStr">
         <is>
           <t>https://www.qhrd.gov.cn</t>
         </is>
       </c>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
-      <c r="O28" t="inlineStr"/>
-      <c r="P28" t="inlineStr"/>
-      <c r="Q28" t="inlineStr"/>
-      <c r="R28" t="inlineStr"/>
-      <c r="S28" t="inlineStr"/>
-      <c r="T28" t="inlineStr"/>
-      <c r="U28" t="inlineStr"/>
-      <c r="V28" t="inlineStr"/>
-      <c r="W28" t="inlineStr"/>
-      <c r="X28" t="inlineStr"/>
-      <c r="Y28" t="inlineStr"/>
-      <c r="Z28" t="inlineStr"/>
-      <c r="AA28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
         <v>27</v>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="C29" t="inlineStr">
         <is>
           <t>自治区</t>
         </is>
       </c>
-      <c r="C29" t="n">
-        <v>1</v>
-      </c>
-      <c r="D29" t="inlineStr">
+      <c r="D29" t="n">
+        <v>1</v>
+      </c>
+      <c r="E29" t="inlineStr">
         <is>
           <t>内蒙古自治区人民代表大会常务委员会</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
+      <c r="F29" t="inlineStr">
         <is>
           <t>内蒙古自治区人民代表大会常设机关，发布地方立法、监督与代表工作信息。</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr">
+      <c r="H29" t="inlineStr">
         <is>
           <t>人大,内蒙古,自治区</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
+      <c r="L29" t="inlineStr">
         <is>
           <t>访问官网 - www.nmgrd.gov.cn</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr">
+      <c r="M29" t="inlineStr">
         <is>
           <t>https://www.nmgrd.gov.cn</t>
         </is>
       </c>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
-      <c r="O29" t="inlineStr"/>
-      <c r="P29" t="inlineStr"/>
-      <c r="Q29" t="inlineStr"/>
-      <c r="R29" t="inlineStr"/>
-      <c r="S29" t="inlineStr"/>
-      <c r="T29" t="inlineStr"/>
-      <c r="U29" t="inlineStr"/>
-      <c r="V29" t="inlineStr"/>
-      <c r="W29" t="inlineStr"/>
-      <c r="X29" t="inlineStr"/>
-      <c r="Y29" t="inlineStr"/>
-      <c r="Z29" t="inlineStr"/>
-      <c r="AA29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
         <v>28</v>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="C30" t="inlineStr">
         <is>
           <t>自治区</t>
         </is>
       </c>
-      <c r="C30" t="n">
-        <v>1</v>
-      </c>
-      <c r="D30" t="inlineStr">
+      <c r="D30" t="n">
+        <v>1</v>
+      </c>
+      <c r="E30" t="inlineStr">
         <is>
           <t>广西壮族自治区人民代表大会常务委员会</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
+      <c r="F30" t="inlineStr">
         <is>
           <t>广西壮族自治区人民代表大会常设机关，发布地方立法与代表履职信息。</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr"/>
-      <c r="G30" t="inlineStr">
+      <c r="H30" t="inlineStr">
         <is>
           <t>人大,广西,自治区</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
+      <c r="L30" t="inlineStr">
         <is>
           <t>访问官网 - www.gxrd.gov.cn</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
+      <c r="M30" t="inlineStr">
         <is>
           <t>https://www.gxrd.gov.cn</t>
         </is>
       </c>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
-      <c r="O30" t="inlineStr"/>
-      <c r="P30" t="inlineStr"/>
-      <c r="Q30" t="inlineStr"/>
-      <c r="R30" t="inlineStr"/>
-      <c r="S30" t="inlineStr"/>
-      <c r="T30" t="inlineStr"/>
-      <c r="U30" t="inlineStr"/>
-      <c r="V30" t="inlineStr"/>
-      <c r="W30" t="inlineStr"/>
-      <c r="X30" t="inlineStr"/>
-      <c r="Y30" t="inlineStr"/>
-      <c r="Z30" t="inlineStr"/>
-      <c r="AA30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
         <v>29</v>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="C31" t="inlineStr">
         <is>
           <t>自治区</t>
         </is>
       </c>
-      <c r="C31" t="n">
-        <v>1</v>
-      </c>
-      <c r="D31" t="inlineStr">
+      <c r="D31" t="n">
+        <v>1</v>
+      </c>
+      <c r="E31" t="inlineStr">
         <is>
           <t>西藏自治区人民代表大会常务委员会</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
+      <c r="F31" t="inlineStr">
         <is>
           <t>西藏自治区人民代表大会常设机关，发布地方立法与监督信息。</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr"/>
-      <c r="G31" t="inlineStr">
+      <c r="H31" t="inlineStr">
         <is>
           <t>人大,西藏,自治区</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
+      <c r="L31" t="inlineStr">
         <is>
           <t>访问官网 - www.xizangrd.gov.cn</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
+      <c r="M31" t="inlineStr">
         <is>
           <t>https://www.xizangrd.gov.cn</t>
         </is>
       </c>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
-      <c r="O31" t="inlineStr"/>
-      <c r="P31" t="inlineStr"/>
-      <c r="Q31" t="inlineStr"/>
-      <c r="R31" t="inlineStr"/>
-      <c r="S31" t="inlineStr"/>
-      <c r="T31" t="inlineStr"/>
-      <c r="U31" t="inlineStr"/>
-      <c r="V31" t="inlineStr"/>
-      <c r="W31" t="inlineStr"/>
-      <c r="X31" t="inlineStr"/>
-      <c r="Y31" t="inlineStr"/>
-      <c r="Z31" t="inlineStr"/>
-      <c r="AA31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
         <v>30</v>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="C32" t="inlineStr">
         <is>
           <t>自治区</t>
         </is>
       </c>
-      <c r="C32" t="n">
-        <v>1</v>
-      </c>
-      <c r="D32" t="inlineStr">
+      <c r="D32" t="n">
+        <v>1</v>
+      </c>
+      <c r="E32" t="inlineStr">
         <is>
           <t>宁夏回族自治区人民代表大会常务委员会</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
+      <c r="F32" t="inlineStr">
         <is>
           <t>宁夏回族自治区人民代表大会常设机关，发布地方性法规与代表工作信息。</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr"/>
-      <c r="G32" t="inlineStr">
+      <c r="H32" t="inlineStr">
         <is>
           <t>人大,宁夏,自治区</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
+      <c r="L32" t="inlineStr">
         <is>
           <t>访问官网 - www.nxrd.gov.cn</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
+      <c r="M32" t="inlineStr">
         <is>
           <t>https://www.nxrd.gov.cn</t>
         </is>
       </c>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
-      <c r="O32" t="inlineStr"/>
-      <c r="P32" t="inlineStr"/>
-      <c r="Q32" t="inlineStr"/>
-      <c r="R32" t="inlineStr"/>
-      <c r="S32" t="inlineStr"/>
-      <c r="T32" t="inlineStr"/>
-      <c r="U32" t="inlineStr"/>
-      <c r="V32" t="inlineStr"/>
-      <c r="W32" t="inlineStr"/>
-      <c r="X32" t="inlineStr"/>
-      <c r="Y32" t="inlineStr"/>
-      <c r="Z32" t="inlineStr"/>
-      <c r="AA32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
         <v>31</v>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="C33" t="inlineStr">
         <is>
           <t>自治区</t>
         </is>
       </c>
-      <c r="C33" t="n">
-        <v>1</v>
-      </c>
-      <c r="D33" t="inlineStr">
+      <c r="D33" t="n">
+        <v>1</v>
+      </c>
+      <c r="E33" t="inlineStr">
         <is>
           <t>新疆维吾尔自治区人民代表大会常务委员会</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
+      <c r="F33" t="inlineStr">
         <is>
           <t>新疆维吾尔自治区人民代表大会常设机关，发布地方立法、监督与代表工作信息。</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr"/>
-      <c r="G33" t="inlineStr">
+      <c r="H33" t="inlineStr">
         <is>
           <t>人大,新疆,自治区</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
+      <c r="L33" t="inlineStr">
         <is>
           <t>访问官网 - www.xjpcsc.gov.cn</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
+      <c r="M33" t="inlineStr">
         <is>
           <t>https://www.xjpcsc.gov.cn</t>
         </is>
       </c>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
-      <c r="O33" t="inlineStr"/>
-      <c r="P33" t="inlineStr"/>
-      <c r="Q33" t="inlineStr"/>
-      <c r="R33" t="inlineStr"/>
-      <c r="S33" t="inlineStr"/>
-      <c r="T33" t="inlineStr"/>
-      <c r="U33" t="inlineStr"/>
-      <c r="V33" t="inlineStr"/>
-      <c r="W33" t="inlineStr"/>
-      <c r="X33" t="inlineStr"/>
-      <c r="Y33" t="inlineStr"/>
-      <c r="Z33" t="inlineStr"/>
-      <c r="AA33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
         <v>32</v>
       </c>
-      <c r="B34" t="inlineStr">
+      <c r="C34" t="inlineStr">
         <is>
           <t>国务院</t>
         </is>
       </c>
-      <c r="C34" t="n">
-        <v>1</v>
-      </c>
-      <c r="D34" t="inlineStr">
+      <c r="D34" t="n">
+        <v>1</v>
+      </c>
+      <c r="E34" t="inlineStr">
         <is>
           <t>中华人民共和国中央人民政府（国务院）</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
+      <c r="F34" t="inlineStr">
         <is>
           <t>国务院官方网站，国家政务总门户，发布政策法规与政务信息。</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr"/>
-      <c r="G34" t="inlineStr">
+      <c r="H34" t="inlineStr">
         <is>
           <t>政务,国务院,中央政府</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
+      <c r="L34" t="inlineStr">
         <is>
           <t>访问官网 - www.gov.cn</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr">
+      <c r="M34" t="inlineStr">
         <is>
           <t>https://www.gov.cn</t>
         </is>
       </c>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
-      <c r="O34" t="inlineStr"/>
-      <c r="P34" t="inlineStr"/>
-      <c r="Q34" t="inlineStr"/>
-      <c r="R34" t="inlineStr"/>
-      <c r="S34" t="inlineStr"/>
-      <c r="T34" t="inlineStr"/>
-      <c r="U34" t="inlineStr"/>
-      <c r="V34" t="inlineStr"/>
-      <c r="W34" t="inlineStr"/>
-      <c r="X34" t="inlineStr"/>
-      <c r="Y34" t="inlineStr"/>
-      <c r="Z34" t="inlineStr"/>
-      <c r="AA34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
         <v>33</v>
       </c>
-      <c r="B35" t="inlineStr">
+      <c r="C35" t="inlineStr">
         <is>
           <t>国家平台</t>
         </is>
       </c>
-      <c r="C35" t="n">
-        <v>1</v>
-      </c>
-      <c r="D35" t="inlineStr">
+      <c r="D35" t="n">
+        <v>1</v>
+      </c>
+      <c r="E35" t="inlineStr">
         <is>
           <t>国家政务服务平台</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr">
+      <c r="F35" t="inlineStr">
         <is>
           <t>全国统一政务服务平台，提供在线办事、政务服务与效能监督。</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr"/>
-      <c r="G35" t="inlineStr">
+      <c r="H35" t="inlineStr">
         <is>
           <t>政务,服务平台,在线办事</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
+      <c r="L35" t="inlineStr">
         <is>
           <t>访问官网 - gjzwfw.www.gov.cn</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr">
+      <c r="M35" t="inlineStr">
         <is>
           <t>https://gjzwfw.www.gov.cn</t>
         </is>
       </c>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
-      <c r="O35" t="inlineStr"/>
-      <c r="P35" t="inlineStr"/>
-      <c r="Q35" t="inlineStr"/>
-      <c r="R35" t="inlineStr"/>
-      <c r="S35" t="inlineStr"/>
-      <c r="T35" t="inlineStr"/>
-      <c r="U35" t="inlineStr"/>
-      <c r="V35" t="inlineStr"/>
-      <c r="W35" t="inlineStr"/>
-      <c r="X35" t="inlineStr"/>
-      <c r="Y35" t="inlineStr"/>
-      <c r="Z35" t="inlineStr"/>
-      <c r="AA35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
         <v>34</v>
       </c>
-      <c r="B36" t="inlineStr">
+      <c r="C36" t="inlineStr">
         <is>
           <t>组成部门</t>
         </is>
       </c>
-      <c r="C36" t="n">
-        <v>1</v>
-      </c>
-      <c r="D36" t="inlineStr">
+      <c r="D36" t="n">
+        <v>1</v>
+      </c>
+      <c r="E36" t="inlineStr">
         <is>
           <t>外交部</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
+      <c r="F36" t="inlineStr">
         <is>
           <t>主管外交事务，发布外交政策、双边关系与国际交往信息。</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr"/>
-      <c r="G36" t="inlineStr">
+      <c r="H36" t="inlineStr">
         <is>
           <t>政务,外交,外交部</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
+      <c r="L36" t="inlineStr">
         <is>
           <t>访问官网 - www.mfa.gov.cn</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr">
+      <c r="M36" t="inlineStr">
         <is>
           <t>https://www.mfa.gov.cn</t>
         </is>
       </c>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
-      <c r="O36" t="inlineStr"/>
-      <c r="P36" t="inlineStr"/>
-      <c r="Q36" t="inlineStr"/>
-      <c r="R36" t="inlineStr"/>
-      <c r="S36" t="inlineStr"/>
-      <c r="T36" t="inlineStr"/>
-      <c r="U36" t="inlineStr"/>
-      <c r="V36" t="inlineStr"/>
-      <c r="W36" t="inlineStr"/>
-      <c r="X36" t="inlineStr"/>
-      <c r="Y36" t="inlineStr"/>
-      <c r="Z36" t="inlineStr"/>
-      <c r="AA36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
         <v>35</v>
       </c>
-      <c r="B37" t="inlineStr">
+      <c r="C37" t="inlineStr">
         <is>
           <t>组成部门</t>
         </is>
       </c>
-      <c r="C37" t="n">
-        <v>1</v>
-      </c>
-      <c r="D37" t="inlineStr">
+      <c r="D37" t="n">
+        <v>1</v>
+      </c>
+      <c r="E37" t="inlineStr">
         <is>
           <t>国防部</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
+      <c r="F37" t="inlineStr">
         <is>
           <t>中华人民共和国国防部，发布国防政策、军队建设与权威军事信息。</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr"/>
-      <c r="G37" t="inlineStr">
+      <c r="H37" t="inlineStr">
         <is>
           <t>政务,国防,国防部</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
+      <c r="L37" t="inlineStr">
         <is>
           <t>访问官网 - www.mod.gov.cn</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr">
+      <c r="M37" t="inlineStr">
         <is>
           <t>https://www.mod.gov.cn</t>
         </is>
       </c>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
-      <c r="O37" t="inlineStr"/>
-      <c r="P37" t="inlineStr"/>
-      <c r="Q37" t="inlineStr"/>
-      <c r="R37" t="inlineStr"/>
-      <c r="S37" t="inlineStr"/>
-      <c r="T37" t="inlineStr"/>
-      <c r="U37" t="inlineStr"/>
-      <c r="V37" t="inlineStr"/>
-      <c r="W37" t="inlineStr"/>
-      <c r="X37" t="inlineStr"/>
-      <c r="Y37" t="inlineStr"/>
-      <c r="Z37" t="inlineStr"/>
-      <c r="AA37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
         <v>36</v>
       </c>
-      <c r="B38" t="inlineStr">
+      <c r="C38" t="inlineStr">
         <is>
           <t>组成部门</t>
         </is>
       </c>
-      <c r="C38" t="n">
-        <v>1</v>
-      </c>
-      <c r="D38" t="inlineStr">
+      <c r="D38" t="n">
+        <v>1</v>
+      </c>
+      <c r="E38" t="inlineStr">
         <is>
           <t>国家发展和改革委员会</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr">
+      <c r="F38" t="inlineStr">
         <is>
           <t>宏观经济综合管理，拟订发展战略与规划。</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr"/>
-      <c r="G38" t="inlineStr">
+      <c r="H38" t="inlineStr">
         <is>
           <t>政务,发改委,宏观经济</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
+      <c r="L38" t="inlineStr">
         <is>
           <t>访问官网 - www.ndrc.gov.cn</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr">
+      <c r="M38" t="inlineStr">
         <is>
           <t>https://www.ndrc.gov.cn</t>
         </is>
       </c>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
-      <c r="O38" t="inlineStr"/>
-      <c r="P38" t="inlineStr"/>
-      <c r="Q38" t="inlineStr"/>
-      <c r="R38" t="inlineStr"/>
-      <c r="S38" t="inlineStr"/>
-      <c r="T38" t="inlineStr"/>
-      <c r="U38" t="inlineStr"/>
-      <c r="V38" t="inlineStr"/>
-      <c r="W38" t="inlineStr"/>
-      <c r="X38" t="inlineStr"/>
-      <c r="Y38" t="inlineStr"/>
-      <c r="Z38" t="inlineStr"/>
-      <c r="AA38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
         <v>37</v>
       </c>
-      <c r="B39" t="inlineStr">
+      <c r="C39" t="inlineStr">
         <is>
           <t>组成部门</t>
         </is>
       </c>
-      <c r="C39" t="n">
-        <v>1</v>
-      </c>
-      <c r="D39" t="inlineStr">
+      <c r="D39" t="n">
+        <v>1</v>
+      </c>
+      <c r="E39" t="inlineStr">
         <is>
           <t>教育部</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr">
+      <c r="F39" t="inlineStr">
         <is>
           <t>主管教育事业与语言文字工作，发布教育政策。</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr"/>
-      <c r="G39" t="inlineStr">
+      <c r="H39" t="inlineStr">
         <is>
           <t>政务,教育,教育部</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
+      <c r="L39" t="inlineStr">
         <is>
           <t>访问官网 - www.moe.gov.cn</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr">
+      <c r="M39" t="inlineStr">
         <is>
           <t>https://www.moe.gov.cn</t>
         </is>
       </c>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
-      <c r="O39" t="inlineStr"/>
-      <c r="P39" t="inlineStr"/>
-      <c r="Q39" t="inlineStr"/>
-      <c r="R39" t="inlineStr"/>
-      <c r="S39" t="inlineStr"/>
-      <c r="T39" t="inlineStr"/>
-      <c r="U39" t="inlineStr"/>
-      <c r="V39" t="inlineStr"/>
-      <c r="W39" t="inlineStr"/>
-      <c r="X39" t="inlineStr"/>
-      <c r="Y39" t="inlineStr"/>
-      <c r="Z39" t="inlineStr"/>
-      <c r="AA39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
         <v>38</v>
       </c>
-      <c r="B40" t="inlineStr">
+      <c r="C40" t="inlineStr">
         <is>
           <t>组成部门</t>
         </is>
       </c>
-      <c r="C40" t="n">
-        <v>1</v>
-      </c>
-      <c r="D40" t="inlineStr">
+      <c r="D40" t="n">
+        <v>1</v>
+      </c>
+      <c r="E40" t="inlineStr">
         <is>
           <t>科学技术部</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr">
+      <c r="F40" t="inlineStr">
         <is>
           <t>主管科技发展与创新，发布科技政策与研发计划信息。</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr"/>
-      <c r="G40" t="inlineStr">
+      <c r="H40" t="inlineStr">
         <is>
           <t>政务,科技,科技部</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
+      <c r="L40" t="inlineStr">
         <is>
           <t>访问官网 - www.most.gov.cn</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr">
+      <c r="M40" t="inlineStr">
         <is>
           <t>https://www.most.gov.cn</t>
         </is>
       </c>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
-      <c r="O40" t="inlineStr"/>
-      <c r="P40" t="inlineStr"/>
-      <c r="Q40" t="inlineStr"/>
-      <c r="R40" t="inlineStr"/>
-      <c r="S40" t="inlineStr"/>
-      <c r="T40" t="inlineStr"/>
-      <c r="U40" t="inlineStr"/>
-      <c r="V40" t="inlineStr"/>
-      <c r="W40" t="inlineStr"/>
-      <c r="X40" t="inlineStr"/>
-      <c r="Y40" t="inlineStr"/>
-      <c r="Z40" t="inlineStr"/>
-      <c r="AA40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
         <v>39</v>
       </c>
-      <c r="B41" t="inlineStr">
+      <c r="C41" t="inlineStr">
         <is>
           <t>组成部门</t>
         </is>
       </c>
-      <c r="C41" t="n">
-        <v>1</v>
-      </c>
-      <c r="D41" t="inlineStr">
+      <c r="D41" t="n">
+        <v>1</v>
+      </c>
+      <c r="E41" t="inlineStr">
         <is>
           <t>工业和信息化部</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
+      <c r="F41" t="inlineStr">
         <is>
           <t>主管工业与信息化产业发展与行业管理。</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr"/>
-      <c r="G41" t="inlineStr">
+      <c r="H41" t="inlineStr">
         <is>
           <t>政务,工信,信息化</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
+      <c r="L41" t="inlineStr">
         <is>
           <t>访问官网 - www.miit.gov.cn</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr">
+      <c r="M41" t="inlineStr">
         <is>
           <t>https://www.miit.gov.cn</t>
         </is>
       </c>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
-      <c r="O41" t="inlineStr"/>
-      <c r="P41" t="inlineStr"/>
-      <c r="Q41" t="inlineStr"/>
-      <c r="R41" t="inlineStr"/>
-      <c r="S41" t="inlineStr"/>
-      <c r="T41" t="inlineStr"/>
-      <c r="U41" t="inlineStr"/>
-      <c r="V41" t="inlineStr"/>
-      <c r="W41" t="inlineStr"/>
-      <c r="X41" t="inlineStr"/>
-      <c r="Y41" t="inlineStr"/>
-      <c r="Z41" t="inlineStr"/>
-      <c r="AA41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
         <v>40</v>
       </c>
-      <c r="B42" t="inlineStr">
+      <c r="C42" t="inlineStr">
         <is>
           <t>组成部门</t>
         </is>
       </c>
-      <c r="C42" t="n">
-        <v>1</v>
-      </c>
-      <c r="D42" t="inlineStr">
+      <c r="D42" t="n">
+        <v>1</v>
+      </c>
+      <c r="E42" t="inlineStr">
         <is>
           <t>国家民族事务委员会</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr">
+      <c r="F42" t="inlineStr">
         <is>
           <t>主管民族事务与民族团结进步工作，发布民族政策信息。</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr"/>
-      <c r="G42" t="inlineStr">
+      <c r="H42" t="inlineStr">
         <is>
           <t>政务,民委,民族事务</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
+      <c r="L42" t="inlineStr">
         <is>
           <t>访问官网 - www.neac.gov.cn</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr">
+      <c r="M42" t="inlineStr">
         <is>
           <t>https://www.neac.gov.cn</t>
         </is>
       </c>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr"/>
-      <c r="N42" t="inlineStr"/>
-      <c r="O42" t="inlineStr"/>
-      <c r="P42" t="inlineStr"/>
-      <c r="Q42" t="inlineStr"/>
-      <c r="R42" t="inlineStr"/>
-      <c r="S42" t="inlineStr"/>
-      <c r="T42" t="inlineStr"/>
-      <c r="U42" t="inlineStr"/>
-      <c r="V42" t="inlineStr"/>
-      <c r="W42" t="inlineStr"/>
-      <c r="X42" t="inlineStr"/>
-      <c r="Y42" t="inlineStr"/>
-      <c r="Z42" t="inlineStr"/>
-      <c r="AA42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
         <v>41</v>
       </c>
-      <c r="B43" t="inlineStr">
+      <c r="C43" t="inlineStr">
         <is>
           <t>组成部门</t>
         </is>
       </c>
-      <c r="C43" t="n">
-        <v>1</v>
-      </c>
-      <c r="D43" t="inlineStr">
+      <c r="D43" t="n">
+        <v>1</v>
+      </c>
+      <c r="E43" t="inlineStr">
         <is>
           <t>公安部</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr">
+      <c r="F43" t="inlineStr">
         <is>
           <t>维护社会治安，主管公安工作。</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr"/>
-      <c r="G43" t="inlineStr">
+      <c r="H43" t="inlineStr">
         <is>
           <t>政务,公安,公安部</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
+      <c r="L43" t="inlineStr">
         <is>
           <t>访问官网 - www.mps.gov.cn</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr">
+      <c r="M43" t="inlineStr">
         <is>
           <t>https://www.mps.gov.cn</t>
         </is>
       </c>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
-      <c r="O43" t="inlineStr"/>
-      <c r="P43" t="inlineStr"/>
-      <c r="Q43" t="inlineStr"/>
-      <c r="R43" t="inlineStr"/>
-      <c r="S43" t="inlineStr"/>
-      <c r="T43" t="inlineStr"/>
-      <c r="U43" t="inlineStr"/>
-      <c r="V43" t="inlineStr"/>
-      <c r="W43" t="inlineStr"/>
-      <c r="X43" t="inlineStr"/>
-      <c r="Y43" t="inlineStr"/>
-      <c r="Z43" t="inlineStr"/>
-      <c r="AA43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
         <v>42</v>
       </c>
-      <c r="B44" t="inlineStr">
+      <c r="C44" t="inlineStr">
         <is>
           <t>组成部门</t>
         </is>
       </c>
-      <c r="C44" t="n">
-        <v>1</v>
-      </c>
-      <c r="D44" t="inlineStr">
+      <c r="D44" t="n">
+        <v>1</v>
+      </c>
+      <c r="E44" t="inlineStr">
         <is>
           <t>民政部</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr">
+      <c r="F44" t="inlineStr">
         <is>
           <t>主管民政事务、社会救助与社会组织管理。</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr"/>
-      <c r="G44" t="inlineStr">
+      <c r="H44" t="inlineStr">
         <is>
           <t>政务,民政,民政部</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
+      <c r="L44" t="inlineStr">
         <is>
           <t>访问官网 - www.mca.gov.cn</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr">
+      <c r="M44" t="inlineStr">
         <is>
           <t>https://www.mca.gov.cn</t>
         </is>
       </c>
-      <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr"/>
-      <c r="N44" t="inlineStr"/>
-      <c r="O44" t="inlineStr"/>
-      <c r="P44" t="inlineStr"/>
-      <c r="Q44" t="inlineStr"/>
-      <c r="R44" t="inlineStr"/>
-      <c r="S44" t="inlineStr"/>
-      <c r="T44" t="inlineStr"/>
-      <c r="U44" t="inlineStr"/>
-      <c r="V44" t="inlineStr"/>
-      <c r="W44" t="inlineStr"/>
-      <c r="X44" t="inlineStr"/>
-      <c r="Y44" t="inlineStr"/>
-      <c r="Z44" t="inlineStr"/>
-      <c r="AA44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
         <v>43</v>
       </c>
-      <c r="B45" t="inlineStr">
+      <c r="C45" t="inlineStr">
         <is>
           <t>组成部门</t>
         </is>
       </c>
-      <c r="C45" t="n">
-        <v>1</v>
-      </c>
-      <c r="D45" t="inlineStr">
+      <c r="D45" t="n">
+        <v>1</v>
+      </c>
+      <c r="E45" t="inlineStr">
         <is>
           <t>司法部</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr">
+      <c r="F45" t="inlineStr">
         <is>
           <t>主管司法行政、法治建设与法律服务。</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr"/>
-      <c r="G45" t="inlineStr">
+      <c r="H45" t="inlineStr">
         <is>
           <t>政务,司法,司法部</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
+      <c r="L45" t="inlineStr">
         <is>
           <t>访问官网 - www.moj.gov.cn</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr">
+      <c r="M45" t="inlineStr">
         <is>
           <t>https://www.moj.gov.cn</t>
         </is>
       </c>
-      <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
-      <c r="O45" t="inlineStr"/>
-      <c r="P45" t="inlineStr"/>
-      <c r="Q45" t="inlineStr"/>
-      <c r="R45" t="inlineStr"/>
-      <c r="S45" t="inlineStr"/>
-      <c r="T45" t="inlineStr"/>
-      <c r="U45" t="inlineStr"/>
-      <c r="V45" t="inlineStr"/>
-      <c r="W45" t="inlineStr"/>
-      <c r="X45" t="inlineStr"/>
-      <c r="Y45" t="inlineStr"/>
-      <c r="Z45" t="inlineStr"/>
-      <c r="AA45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
         <v>44</v>
       </c>
-      <c r="B46" t="inlineStr">
+      <c r="C46" t="inlineStr">
         <is>
           <t>组成部门</t>
         </is>
       </c>
-      <c r="C46" t="n">
-        <v>1</v>
-      </c>
-      <c r="D46" t="inlineStr">
+      <c r="D46" t="n">
+        <v>1</v>
+      </c>
+      <c r="E46" t="inlineStr">
         <is>
           <t>财政部</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr">
+      <c r="F46" t="inlineStr">
         <is>
           <t>主管国家财政收支与财税政策。</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr"/>
-      <c r="G46" t="inlineStr">
+      <c r="H46" t="inlineStr">
         <is>
           <t>政务,财政,财政部</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
+      <c r="L46" t="inlineStr">
         <is>
           <t>访问官网 - www.mof.gov.cn</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr">
+      <c r="M46" t="inlineStr">
         <is>
           <t>https://www.mof.gov.cn</t>
         </is>
       </c>
-      <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr"/>
-      <c r="N46" t="inlineStr"/>
-      <c r="O46" t="inlineStr"/>
-      <c r="P46" t="inlineStr"/>
-      <c r="Q46" t="inlineStr"/>
-      <c r="R46" t="inlineStr"/>
-      <c r="S46" t="inlineStr"/>
-      <c r="T46" t="inlineStr"/>
-      <c r="U46" t="inlineStr"/>
-      <c r="V46" t="inlineStr"/>
-      <c r="W46" t="inlineStr"/>
-      <c r="X46" t="inlineStr"/>
-      <c r="Y46" t="inlineStr"/>
-      <c r="Z46" t="inlineStr"/>
-      <c r="AA46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
         <v>45</v>
       </c>
-      <c r="B47" t="inlineStr">
+      <c r="C47" t="inlineStr">
         <is>
           <t>组成部门</t>
         </is>
       </c>
-      <c r="C47" t="n">
-        <v>1</v>
-      </c>
-      <c r="D47" t="inlineStr">
+      <c r="D47" t="n">
+        <v>1</v>
+      </c>
+      <c r="E47" t="inlineStr">
         <is>
           <t>人力资源和社会保障部</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr">
+      <c r="F47" t="inlineStr">
         <is>
           <t>主管就业、社保与人事人才工作。</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr"/>
-      <c r="G47" t="inlineStr">
+      <c r="H47" t="inlineStr">
         <is>
           <t>政务,人社,社保</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
+      <c r="L47" t="inlineStr">
         <is>
           <t>访问官网 - www.mohrss.gov.cn</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr">
+      <c r="M47" t="inlineStr">
         <is>
           <t>https://www.mohrss.gov.cn</t>
         </is>
       </c>
-      <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr"/>
-      <c r="N47" t="inlineStr"/>
-      <c r="O47" t="inlineStr"/>
-      <c r="P47" t="inlineStr"/>
-      <c r="Q47" t="inlineStr"/>
-      <c r="R47" t="inlineStr"/>
-      <c r="S47" t="inlineStr"/>
-      <c r="T47" t="inlineStr"/>
-      <c r="U47" t="inlineStr"/>
-      <c r="V47" t="inlineStr"/>
-      <c r="W47" t="inlineStr"/>
-      <c r="X47" t="inlineStr"/>
-      <c r="Y47" t="inlineStr"/>
-      <c r="Z47" t="inlineStr"/>
-      <c r="AA47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
         <v>46</v>
       </c>
-      <c r="B48" t="inlineStr">
+      <c r="C48" t="inlineStr">
         <is>
           <t>组成部门</t>
         </is>
       </c>
-      <c r="C48" t="n">
-        <v>1</v>
-      </c>
-      <c r="D48" t="inlineStr">
+      <c r="D48" t="n">
+        <v>1</v>
+      </c>
+      <c r="E48" t="inlineStr">
         <is>
           <t>自然资源部</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr">
+      <c r="F48" t="inlineStr">
         <is>
           <t>主管自然资源调查、规划与确权登记。</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr"/>
-      <c r="G48" t="inlineStr">
+      <c r="H48" t="inlineStr">
         <is>
           <t>政务,自然资源,国土</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
+      <c r="L48" t="inlineStr">
         <is>
           <t>访问官网 - www.mnr.gov.cn</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr">
+      <c r="M48" t="inlineStr">
         <is>
           <t>https://www.mnr.gov.cn</t>
         </is>
       </c>
-      <c r="J48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr"/>
-      <c r="N48" t="inlineStr"/>
-      <c r="O48" t="inlineStr"/>
-      <c r="P48" t="inlineStr"/>
-      <c r="Q48" t="inlineStr"/>
-      <c r="R48" t="inlineStr"/>
-      <c r="S48" t="inlineStr"/>
-      <c r="T48" t="inlineStr"/>
-      <c r="U48" t="inlineStr"/>
-      <c r="V48" t="inlineStr"/>
-      <c r="W48" t="inlineStr"/>
-      <c r="X48" t="inlineStr"/>
-      <c r="Y48" t="inlineStr"/>
-      <c r="Z48" t="inlineStr"/>
-      <c r="AA48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
         <v>47</v>
       </c>
-      <c r="B49" t="inlineStr">
+      <c r="C49" t="inlineStr">
         <is>
           <t>组成部门</t>
         </is>
       </c>
-      <c r="C49" t="n">
-        <v>1</v>
-      </c>
-      <c r="D49" t="inlineStr">
+      <c r="D49" t="n">
+        <v>1</v>
+      </c>
+      <c r="E49" t="inlineStr">
         <is>
           <t>生态环境部</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr">
+      <c r="F49" t="inlineStr">
         <is>
           <t>主管生态环境保护的监督管理。</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr"/>
-      <c r="G49" t="inlineStr">
+      <c r="H49" t="inlineStr">
         <is>
           <t>政务,生态环境,环保</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
+      <c r="L49" t="inlineStr">
         <is>
           <t>访问官网 - www.mee.gov.cn</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr">
+      <c r="M49" t="inlineStr">
         <is>
           <t>https://www.mee.gov.cn</t>
         </is>
       </c>
-      <c r="J49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr"/>
-      <c r="N49" t="inlineStr"/>
-      <c r="O49" t="inlineStr"/>
-      <c r="P49" t="inlineStr"/>
-      <c r="Q49" t="inlineStr"/>
-      <c r="R49" t="inlineStr"/>
-      <c r="S49" t="inlineStr"/>
-      <c r="T49" t="inlineStr"/>
-      <c r="U49" t="inlineStr"/>
-      <c r="V49" t="inlineStr"/>
-      <c r="W49" t="inlineStr"/>
-      <c r="X49" t="inlineStr"/>
-      <c r="Y49" t="inlineStr"/>
-      <c r="Z49" t="inlineStr"/>
-      <c r="AA49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
         <v>48</v>
       </c>
-      <c r="B50" t="inlineStr">
+      <c r="C50" t="inlineStr">
         <is>
           <t>组成部门</t>
         </is>
       </c>
-      <c r="C50" t="n">
-        <v>1</v>
-      </c>
-      <c r="D50" t="inlineStr">
+      <c r="D50" t="n">
+        <v>1</v>
+      </c>
+      <c r="E50" t="inlineStr">
         <is>
           <t>住房和城乡建设部</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr">
+      <c r="F50" t="inlineStr">
         <is>
           <t>主管住房保障与城乡建设，发布建筑市场与市政建设政策。</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr"/>
-      <c r="G50" t="inlineStr">
+      <c r="H50" t="inlineStr">
         <is>
           <t>政务,住建,城乡建设</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
+      <c r="L50" t="inlineStr">
         <is>
           <t>访问官网 - www.mohurd.gov.cn</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr">
+      <c r="M50" t="inlineStr">
         <is>
           <t>https://www.mohurd.gov.cn</t>
         </is>
       </c>
-      <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr"/>
-      <c r="N50" t="inlineStr"/>
-      <c r="O50" t="inlineStr"/>
-      <c r="P50" t="inlineStr"/>
-      <c r="Q50" t="inlineStr"/>
-      <c r="R50" t="inlineStr"/>
-      <c r="S50" t="inlineStr"/>
-      <c r="T50" t="inlineStr"/>
-      <c r="U50" t="inlineStr"/>
-      <c r="V50" t="inlineStr"/>
-      <c r="W50" t="inlineStr"/>
-      <c r="X50" t="inlineStr"/>
-      <c r="Y50" t="inlineStr"/>
-      <c r="Z50" t="inlineStr"/>
-      <c r="AA50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
         <v>49</v>
       </c>
-      <c r="B51" t="inlineStr">
+      <c r="C51" t="inlineStr">
         <is>
           <t>组成部门</t>
         </is>
       </c>
-      <c r="C51" t="n">
-        <v>1</v>
-      </c>
-      <c r="D51" t="inlineStr">
+      <c r="D51" t="n">
+        <v>1</v>
+      </c>
+      <c r="E51" t="inlineStr">
         <is>
           <t>交通运输部</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr">
+      <c r="F51" t="inlineStr">
         <is>
           <t>主管公路、水路、铁路等综合交通运输。</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr"/>
-      <c r="G51" t="inlineStr">
+      <c r="H51" t="inlineStr">
         <is>
           <t>政务,交通,运输</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
+      <c r="L51" t="inlineStr">
         <is>
           <t>访问官网 - www.mot.gov.cn</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr">
+      <c r="M51" t="inlineStr">
         <is>
           <t>https://www.mot.gov.cn</t>
         </is>
       </c>
-      <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr"/>
-      <c r="N51" t="inlineStr"/>
-      <c r="O51" t="inlineStr"/>
-      <c r="P51" t="inlineStr"/>
-      <c r="Q51" t="inlineStr"/>
-      <c r="R51" t="inlineStr"/>
-      <c r="S51" t="inlineStr"/>
-      <c r="T51" t="inlineStr"/>
-      <c r="U51" t="inlineStr"/>
-      <c r="V51" t="inlineStr"/>
-      <c r="W51" t="inlineStr"/>
-      <c r="X51" t="inlineStr"/>
-      <c r="Y51" t="inlineStr"/>
-      <c r="Z51" t="inlineStr"/>
-      <c r="AA51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
         <v>50</v>
       </c>
-      <c r="B52" t="inlineStr">
+      <c r="C52" t="inlineStr">
         <is>
           <t>组成部门</t>
         </is>
       </c>
-      <c r="C52" t="n">
-        <v>1</v>
-      </c>
-      <c r="D52" t="inlineStr">
+      <c r="D52" t="n">
+        <v>1</v>
+      </c>
+      <c r="E52" t="inlineStr">
         <is>
           <t>水利部</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr">
+      <c r="F52" t="inlineStr">
         <is>
           <t>主管水资源管理与水利建设，发布防汛抗旱与河湖治理信息。</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr"/>
-      <c r="G52" t="inlineStr">
+      <c r="H52" t="inlineStr">
         <is>
           <t>政务,水利,水资源</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
+      <c r="L52" t="inlineStr">
         <is>
           <t>访问官网 - www.mwr.gov.cn</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr">
+      <c r="M52" t="inlineStr">
         <is>
           <t>https://www.mwr.gov.cn</t>
         </is>
       </c>
-      <c r="J52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
-      <c r="O52" t="inlineStr"/>
-      <c r="P52" t="inlineStr"/>
-      <c r="Q52" t="inlineStr"/>
-      <c r="R52" t="inlineStr"/>
-      <c r="S52" t="inlineStr"/>
-      <c r="T52" t="inlineStr"/>
-      <c r="U52" t="inlineStr"/>
-      <c r="V52" t="inlineStr"/>
-      <c r="W52" t="inlineStr"/>
-      <c r="X52" t="inlineStr"/>
-      <c r="Y52" t="inlineStr"/>
-      <c r="Z52" t="inlineStr"/>
-      <c r="AA52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
         <v>51</v>
       </c>
-      <c r="B53" t="inlineStr">
+      <c r="C53" t="inlineStr">
         <is>
           <t>组成部门</t>
         </is>
       </c>
-      <c r="C53" t="n">
-        <v>1</v>
-      </c>
-      <c r="D53" t="inlineStr">
+      <c r="D53" t="n">
+        <v>1</v>
+      </c>
+      <c r="E53" t="inlineStr">
         <is>
           <t>农业农村部</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr">
+      <c r="F53" t="inlineStr">
         <is>
           <t>主管农业农村发展，发布乡村振兴、农业政策与农技信息。</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr"/>
-      <c r="G53" t="inlineStr">
+      <c r="H53" t="inlineStr">
         <is>
           <t>政务,农业,农业农村</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
+      <c r="L53" t="inlineStr">
         <is>
           <t>访问官网 - www.moa.gov.cn</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr">
+      <c r="M53" t="inlineStr">
         <is>
           <t>https://www.moa.gov.cn</t>
         </is>
       </c>
-      <c r="J53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr"/>
-      <c r="N53" t="inlineStr"/>
-      <c r="O53" t="inlineStr"/>
-      <c r="P53" t="inlineStr"/>
-      <c r="Q53" t="inlineStr"/>
-      <c r="R53" t="inlineStr"/>
-      <c r="S53" t="inlineStr"/>
-      <c r="T53" t="inlineStr"/>
-      <c r="U53" t="inlineStr"/>
-      <c r="V53" t="inlineStr"/>
-      <c r="W53" t="inlineStr"/>
-      <c r="X53" t="inlineStr"/>
-      <c r="Y53" t="inlineStr"/>
-      <c r="Z53" t="inlineStr"/>
-      <c r="AA53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
         <v>52</v>
       </c>
-      <c r="B54" t="inlineStr">
+      <c r="C54" t="inlineStr">
         <is>
           <t>组成部门</t>
         </is>
       </c>
-      <c r="C54" t="n">
-        <v>1</v>
-      </c>
-      <c r="D54" t="inlineStr">
+      <c r="D54" t="n">
+        <v>1</v>
+      </c>
+      <c r="E54" t="inlineStr">
         <is>
           <t>商务部</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr">
+      <c r="F54" t="inlineStr">
         <is>
           <t>主管国内外贸易与国际经贸合作，发布商务政策与市场信息。</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr"/>
-      <c r="G54" t="inlineStr">
+      <c r="H54" t="inlineStr">
         <is>
           <t>政务,商务,对外贸易</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
+      <c r="L54" t="inlineStr">
         <is>
           <t>访问官网 - www.mofcom.gov.cn</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr">
+      <c r="M54" t="inlineStr">
         <is>
           <t>https://www.mofcom.gov.cn</t>
         </is>
       </c>
-      <c r="J54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr"/>
-      <c r="N54" t="inlineStr"/>
-      <c r="O54" t="inlineStr"/>
-      <c r="P54" t="inlineStr"/>
-      <c r="Q54" t="inlineStr"/>
-      <c r="R54" t="inlineStr"/>
-      <c r="S54" t="inlineStr"/>
-      <c r="T54" t="inlineStr"/>
-      <c r="U54" t="inlineStr"/>
-      <c r="V54" t="inlineStr"/>
-      <c r="W54" t="inlineStr"/>
-      <c r="X54" t="inlineStr"/>
-      <c r="Y54" t="inlineStr"/>
-      <c r="Z54" t="inlineStr"/>
-      <c r="AA54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
         <v>53</v>
       </c>
-      <c r="B55" t="inlineStr">
+      <c r="C55" t="inlineStr">
         <is>
           <t>组成部门</t>
         </is>
       </c>
-      <c r="C55" t="n">
-        <v>1</v>
-      </c>
-      <c r="D55" t="inlineStr">
+      <c r="D55" t="n">
+        <v>1</v>
+      </c>
+      <c r="E55" t="inlineStr">
         <is>
           <t>文化和旅游部</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr">
+      <c r="F55" t="inlineStr">
         <is>
           <t>主管文化事业与旅游发展，发布文旅政策与公共服务信息。</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr"/>
-      <c r="G55" t="inlineStr">
+      <c r="H55" t="inlineStr">
         <is>
           <t>政务,文旅,文化旅游</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
+      <c r="L55" t="inlineStr">
         <is>
           <t>访问官网 - www.mct.gov.cn</t>
         </is>
       </c>
-      <c r="I55" t="inlineStr">
+      <c r="M55" t="inlineStr">
         <is>
           <t>https://www.mct.gov.cn</t>
         </is>
       </c>
-      <c r="J55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
-      <c r="O55" t="inlineStr"/>
-      <c r="P55" t="inlineStr"/>
-      <c r="Q55" t="inlineStr"/>
-      <c r="R55" t="inlineStr"/>
-      <c r="S55" t="inlineStr"/>
-      <c r="T55" t="inlineStr"/>
-      <c r="U55" t="inlineStr"/>
-      <c r="V55" t="inlineStr"/>
-      <c r="W55" t="inlineStr"/>
-      <c r="X55" t="inlineStr"/>
-      <c r="Y55" t="inlineStr"/>
-      <c r="Z55" t="inlineStr"/>
-      <c r="AA55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
         <v>54</v>
       </c>
-      <c r="B56" t="inlineStr">
+      <c r="C56" t="inlineStr">
         <is>
           <t>组成部门</t>
         </is>
       </c>
-      <c r="C56" t="n">
-        <v>1</v>
-      </c>
-      <c r="D56" t="inlineStr">
+      <c r="D56" t="n">
+        <v>1</v>
+      </c>
+      <c r="E56" t="inlineStr">
         <is>
           <t>国家卫生健康委员会</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr">
+      <c r="F56" t="inlineStr">
         <is>
           <t>主管国民健康与医疗卫生，发布卫生政策与健康服务信息。</t>
         </is>
       </c>
-      <c r="F56" t="inlineStr"/>
-      <c r="G56" t="inlineStr">
+      <c r="H56" t="inlineStr">
         <is>
           <t>政务,卫健,卫生健康</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
+      <c r="L56" t="inlineStr">
         <is>
           <t>访问官网 - www.nhc.gov.cn</t>
         </is>
       </c>
-      <c r="I56" t="inlineStr">
+      <c r="M56" t="inlineStr">
         <is>
           <t>https://www.nhc.gov.cn</t>
         </is>
       </c>
-      <c r="J56" t="inlineStr"/>
-      <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr"/>
-      <c r="N56" t="inlineStr"/>
-      <c r="O56" t="inlineStr"/>
-      <c r="P56" t="inlineStr"/>
-      <c r="Q56" t="inlineStr"/>
-      <c r="R56" t="inlineStr"/>
-      <c r="S56" t="inlineStr"/>
-      <c r="T56" t="inlineStr"/>
-      <c r="U56" t="inlineStr"/>
-      <c r="V56" t="inlineStr"/>
-      <c r="W56" t="inlineStr"/>
-      <c r="X56" t="inlineStr"/>
-      <c r="Y56" t="inlineStr"/>
-      <c r="Z56" t="inlineStr"/>
-      <c r="AA56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
         <v>55</v>
       </c>
-      <c r="B57" t="inlineStr">
+      <c r="C57" t="inlineStr">
         <is>
           <t>组成部门</t>
         </is>
       </c>
-      <c r="C57" t="n">
-        <v>1</v>
-      </c>
-      <c r="D57" t="inlineStr">
+      <c r="D57" t="n">
+        <v>1</v>
+      </c>
+      <c r="E57" t="inlineStr">
         <is>
           <t>退役军人事务部</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr">
+      <c r="F57" t="inlineStr">
         <is>
           <t>主管退役军人优抚安置与服务保障，维护军人军属权益。</t>
         </is>
       </c>
-      <c r="F57" t="inlineStr"/>
-      <c r="G57" t="inlineStr">
+      <c r="H57" t="inlineStr">
         <is>
           <t>政务,退役军人,优抚安置</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
+      <c r="L57" t="inlineStr">
         <is>
           <t>访问官网 - www.mva.gov.cn</t>
         </is>
       </c>
-      <c r="I57" t="inlineStr">
+      <c r="M57" t="inlineStr">
         <is>
           <t>https://www.mva.gov.cn</t>
         </is>
       </c>
-      <c r="J57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr"/>
-      <c r="N57" t="inlineStr"/>
-      <c r="O57" t="inlineStr"/>
-      <c r="P57" t="inlineStr"/>
-      <c r="Q57" t="inlineStr"/>
-      <c r="R57" t="inlineStr"/>
-      <c r="S57" t="inlineStr"/>
-      <c r="T57" t="inlineStr"/>
-      <c r="U57" t="inlineStr"/>
-      <c r="V57" t="inlineStr"/>
-      <c r="W57" t="inlineStr"/>
-      <c r="X57" t="inlineStr"/>
-      <c r="Y57" t="inlineStr"/>
-      <c r="Z57" t="inlineStr"/>
-      <c r="AA57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
         <v>56</v>
       </c>
-      <c r="B58" t="inlineStr">
+      <c r="C58" t="inlineStr">
         <is>
           <t>组成部门</t>
         </is>
       </c>
-      <c r="C58" t="n">
-        <v>1</v>
-      </c>
-      <c r="D58" t="inlineStr">
+      <c r="D58" t="n">
+        <v>1</v>
+      </c>
+      <c r="E58" t="inlineStr">
         <is>
           <t>应急管理部</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr">
+      <c r="F58" t="inlineStr">
         <is>
           <t>主管安全生产与应急救援，发布防灾减灾与事故处置信息。</t>
         </is>
       </c>
-      <c r="F58" t="inlineStr"/>
-      <c r="G58" t="inlineStr">
+      <c r="H58" t="inlineStr">
         <is>
           <t>政务,应急,安全生产</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
+      <c r="L58" t="inlineStr">
         <is>
           <t>访问官网 - www.mem.gov.cn</t>
         </is>
       </c>
-      <c r="I58" t="inlineStr">
+      <c r="M58" t="inlineStr">
         <is>
           <t>https://www.mem.gov.cn</t>
         </is>
       </c>
-      <c r="J58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr"/>
-      <c r="N58" t="inlineStr"/>
-      <c r="O58" t="inlineStr"/>
-      <c r="P58" t="inlineStr"/>
-      <c r="Q58" t="inlineStr"/>
-      <c r="R58" t="inlineStr"/>
-      <c r="S58" t="inlineStr"/>
-      <c r="T58" t="inlineStr"/>
-      <c r="U58" t="inlineStr"/>
-      <c r="V58" t="inlineStr"/>
-      <c r="W58" t="inlineStr"/>
-      <c r="X58" t="inlineStr"/>
-      <c r="Y58" t="inlineStr"/>
-      <c r="Z58" t="inlineStr"/>
-      <c r="AA58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
         <v>57</v>
       </c>
-      <c r="B59" t="inlineStr">
+      <c r="C59" t="inlineStr">
         <is>
           <t>组成部门</t>
         </is>
       </c>
-      <c r="C59" t="n">
-        <v>1</v>
-      </c>
-      <c r="D59" t="inlineStr">
+      <c r="D59" t="n">
+        <v>1</v>
+      </c>
+      <c r="E59" t="inlineStr">
         <is>
           <t>中国人民银行</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr">
+      <c r="F59" t="inlineStr">
         <is>
           <t>中央银行，制定货币政策，维护金融稳定与人民币管理。</t>
         </is>
       </c>
-      <c r="F59" t="inlineStr"/>
-      <c r="G59" t="inlineStr">
+      <c r="H59" t="inlineStr">
         <is>
           <t>政务,央行,货币政策</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr">
+      <c r="L59" t="inlineStr">
         <is>
           <t>访问官网 - www.pbc.gov.cn</t>
         </is>
       </c>
-      <c r="I59" t="inlineStr">
+      <c r="M59" t="inlineStr">
         <is>
           <t>https://www.pbc.gov.cn</t>
         </is>
       </c>
-      <c r="J59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr"/>
-      <c r="N59" t="inlineStr"/>
-      <c r="O59" t="inlineStr"/>
-      <c r="P59" t="inlineStr"/>
-      <c r="Q59" t="inlineStr"/>
-      <c r="R59" t="inlineStr"/>
-      <c r="S59" t="inlineStr"/>
-      <c r="T59" t="inlineStr"/>
-      <c r="U59" t="inlineStr"/>
-      <c r="V59" t="inlineStr"/>
-      <c r="W59" t="inlineStr"/>
-      <c r="X59" t="inlineStr"/>
-      <c r="Y59" t="inlineStr"/>
-      <c r="Z59" t="inlineStr"/>
-      <c r="AA59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
         <v>58</v>
       </c>
-      <c r="B60" t="inlineStr">
+      <c r="C60" t="inlineStr">
         <is>
           <t>组成部门</t>
         </is>
       </c>
-      <c r="C60" t="n">
-        <v>1</v>
-      </c>
-      <c r="D60" t="inlineStr">
+      <c r="D60" t="n">
+        <v>1</v>
+      </c>
+      <c r="E60" t="inlineStr">
         <is>
           <t>审计署</t>
         </is>
       </c>
-      <c r="E60" t="inlineStr">
+      <c r="F60" t="inlineStr">
         <is>
           <t>主管国家财政收支审计监督，发布审计结果与整改信息。</t>
         </is>
       </c>
-      <c r="F60" t="inlineStr"/>
-      <c r="G60" t="inlineStr">
+      <c r="H60" t="inlineStr">
         <is>
           <t>政务,审计,审计监督</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr">
+      <c r="L60" t="inlineStr">
         <is>
           <t>访问官网 - www.audit.gov.cn</t>
         </is>
       </c>
-      <c r="I60" t="inlineStr">
+      <c r="M60" t="inlineStr">
         <is>
           <t>https://www.audit.gov.cn</t>
         </is>
       </c>
-      <c r="J60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr"/>
-      <c r="N60" t="inlineStr"/>
-      <c r="O60" t="inlineStr"/>
-      <c r="P60" t="inlineStr"/>
-      <c r="Q60" t="inlineStr"/>
-      <c r="R60" t="inlineStr"/>
-      <c r="S60" t="inlineStr"/>
-      <c r="T60" t="inlineStr"/>
-      <c r="U60" t="inlineStr"/>
-      <c r="V60" t="inlineStr"/>
-      <c r="W60" t="inlineStr"/>
-      <c r="X60" t="inlineStr"/>
-      <c r="Y60" t="inlineStr"/>
-      <c r="Z60" t="inlineStr"/>
-      <c r="AA60" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/directory/gov/assets/xlsx/self_links.xlsx
+++ b/directory/gov/assets/xlsx/self_links.xlsx
@@ -2,39 +2,375 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="28800" windowHeight="12300" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="links" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="21">
     <font>
-      <name val="Calibri"/>
-      <family val="2"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF0000FF"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF800080"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FFFF0000"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="18"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <i val="1"/>
+      <color rgb="FF7F7F7F"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="15"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="13"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF3F3F76"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FF3F3F3F"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF006100"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF9C0006"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF9C6500"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color theme="0"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -42,15 +378,306 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  <cellStyleXfs count="49">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+  <cellStyles count="49">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
+    <cellStyle name="Currency" xfId="2" builtinId="4"/>
+    <cellStyle name="Percent" xfId="3" builtinId="5"/>
+    <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
+    <cellStyle name="Currency [0]" xfId="5" builtinId="7"/>
+    <cellStyle name="Link" xfId="6" builtinId="8"/>
+    <cellStyle name="Followed Hyperlink" xfId="7" builtinId="9"/>
+    <cellStyle name="Note" xfId="8" builtinId="10"/>
+    <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
+    <cellStyle name="Title" xfId="10" builtinId="15"/>
+    <cellStyle name="Explanatory Text" xfId="11" builtinId="53"/>
+    <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
+    <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
+    <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
+    <cellStyle name="Heading 4" xfId="15" builtinId="19"/>
+    <cellStyle name="Input" xfId="16" builtinId="20"/>
+    <cellStyle name="Output" xfId="17" builtinId="21"/>
+    <cellStyle name="Calculation" xfId="18" builtinId="22"/>
+    <cellStyle name="Check Cell" xfId="19" builtinId="23"/>
+    <cellStyle name="Linked Cell" xfId="20" builtinId="24"/>
+    <cellStyle name="Total" xfId="21" builtinId="25"/>
+    <cellStyle name="Good" xfId="22" builtinId="26"/>
+    <cellStyle name="Bad" xfId="23" builtinId="27"/>
+    <cellStyle name="Neutral" xfId="24" builtinId="28"/>
+    <cellStyle name="Accent1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - Accent1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - Accent1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - Accent1" xfId="28" builtinId="32"/>
+    <cellStyle name="Accent2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - Accent2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - Accent2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - Accent2" xfId="32" builtinId="36"/>
+    <cellStyle name="Accent3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - Accent3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - Accent3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - Accent3" xfId="36" builtinId="40"/>
+    <cellStyle name="Accent4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - Accent4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - Accent4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - Accent4" xfId="40" builtinId="44"/>
+    <cellStyle name="Accent5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - Accent5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - Accent5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - Accent5" xfId="44" builtinId="48"/>
+    <cellStyle name="Accent6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - Accent6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -403,7 +1030,6 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
@@ -413,8 +1039,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB60"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:AE60"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -424,54 +1050,54 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
+          <t>dir_path</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
           <t>cat_id</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>cat_name</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>card_layout</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>card_title</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>card_desc</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>card_media</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>card_tags</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>card_id</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>card_order</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>link_1_id</t>
-        </is>
-      </c>
       <c r="L1" t="inlineStr">
         <is>
           <t>link_1_name</t>
@@ -484,337 +1110,92 @@
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>link_1_desc</t>
+          <t>link_2_name</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>link_1_media</t>
+          <t>link_2_url</t>
         </is>
       </c>
       <c r="P1" t="inlineStr">
         <is>
-          <t>link_1_enabled</t>
+          <t>link_3_name</t>
         </is>
       </c>
       <c r="Q1" t="inlineStr">
         <is>
-          <t>link_2_id</t>
+          <t>link_3_url</t>
         </is>
       </c>
       <c r="R1" t="inlineStr">
         <is>
-          <t>link_2_name</t>
+          <t>link_4_name</t>
         </is>
       </c>
       <c r="S1" t="inlineStr">
         <is>
-          <t>link_2_url</t>
+          <t>link_4_url</t>
         </is>
       </c>
       <c r="T1" t="inlineStr">
         <is>
-          <t>link_2_desc</t>
+          <t>link_5_name</t>
         </is>
       </c>
       <c r="U1" t="inlineStr">
         <is>
-          <t>link_2_media</t>
+          <t>link_5_url</t>
         </is>
       </c>
       <c r="V1" t="inlineStr">
         <is>
-          <t>link_2_enabled</t>
+          <t>link_6_name</t>
         </is>
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>link_3_id</t>
+          <t>link_6_url</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>link_3_name</t>
+          <t>link_7_name</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
         <is>
-          <t>link_3_url</t>
+          <t>link_7_url</t>
         </is>
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>link_3_desc</t>
+          <t>link_8_name</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
         <is>
-          <t>link_3_media</t>
+          <t>link_8_url</t>
         </is>
       </c>
       <c r="AB1" t="inlineStr">
         <is>
-          <t>link_3_enabled</t>
+          <t>link_9_name</t>
         </is>
       </c>
       <c r="AC1" t="inlineStr">
         <is>
-          <t>link_4_id</t>
+          <t>link_9_url</t>
         </is>
       </c>
       <c r="AD1" t="inlineStr">
         <is>
-          <t>link_4_name</t>
+          <t>link_10_name</t>
         </is>
       </c>
       <c r="AE1" t="inlineStr">
         <is>
-          <t>link_4_url</t>
-        </is>
-      </c>
-      <c r="AF1" t="inlineStr">
-        <is>
-          <t>link_4_desc</t>
-        </is>
-      </c>
-      <c r="AG1" t="inlineStr">
-        <is>
-          <t>link_4_media</t>
-        </is>
-      </c>
-      <c r="AH1" t="inlineStr">
-        <is>
-          <t>link_4_enabled</t>
-        </is>
-      </c>
-      <c r="AI1" t="inlineStr">
-        <is>
-          <t>link_5_id</t>
-        </is>
-      </c>
-      <c r="AJ1" t="inlineStr">
-        <is>
-          <t>link_5_name</t>
-        </is>
-      </c>
-      <c r="AK1" t="inlineStr">
-        <is>
-          <t>link_5_url</t>
-        </is>
-      </c>
-      <c r="AL1" t="inlineStr">
-        <is>
-          <t>link_5_desc</t>
-        </is>
-      </c>
-      <c r="AM1" t="inlineStr">
-        <is>
-          <t>link_5_media</t>
-        </is>
-      </c>
-      <c r="AN1" t="inlineStr">
-        <is>
-          <t>link_5_enabled</t>
-        </is>
-      </c>
-      <c r="AO1" t="inlineStr">
-        <is>
-          <t>link_6_id</t>
-        </is>
-      </c>
-      <c r="AP1" t="inlineStr">
-        <is>
-          <t>link_6_name</t>
-        </is>
-      </c>
-      <c r="AQ1" t="inlineStr">
-        <is>
-          <t>link_6_url</t>
-        </is>
-      </c>
-      <c r="AR1" t="inlineStr">
-        <is>
-          <t>link_6_desc</t>
-        </is>
-      </c>
-      <c r="AS1" t="inlineStr">
-        <is>
-          <t>link_6_media</t>
-        </is>
-      </c>
-      <c r="AT1" t="inlineStr">
-        <is>
-          <t>link_6_enabled</t>
-        </is>
-      </c>
-      <c r="AU1" t="inlineStr">
-        <is>
-          <t>link_7_id</t>
-        </is>
-      </c>
-      <c r="AV1" t="inlineStr">
-        <is>
-          <t>link_7_name</t>
-        </is>
-      </c>
-      <c r="AW1" t="inlineStr">
-        <is>
-          <t>link_7_url</t>
-        </is>
-      </c>
-      <c r="AX1" t="inlineStr">
-        <is>
-          <t>link_7_desc</t>
-        </is>
-      </c>
-      <c r="AY1" t="inlineStr">
-        <is>
-          <t>link_7_media</t>
-        </is>
-      </c>
-      <c r="AZ1" t="inlineStr">
-        <is>
-          <t>link_7_enabled</t>
-        </is>
-      </c>
-      <c r="BA1" t="inlineStr">
-        <is>
-          <t>link_8_id</t>
-        </is>
-      </c>
-      <c r="BB1" t="inlineStr">
-        <is>
-          <t>link_8_name</t>
-        </is>
-      </c>
-      <c r="BC1" t="inlineStr">
-        <is>
-          <t>link_8_url</t>
-        </is>
-      </c>
-      <c r="BD1" t="inlineStr">
-        <is>
-          <t>link_8_desc</t>
-        </is>
-      </c>
-      <c r="BE1" t="inlineStr">
-        <is>
-          <t>link_8_media</t>
-        </is>
-      </c>
-      <c r="BF1" t="inlineStr">
-        <is>
-          <t>link_8_enabled</t>
-        </is>
-      </c>
-      <c r="BG1" t="inlineStr">
-        <is>
-          <t>link_9_id</t>
-        </is>
-      </c>
-      <c r="BH1" t="inlineStr">
-        <is>
-          <t>link_9_name</t>
-        </is>
-      </c>
-      <c r="BI1" t="inlineStr">
-        <is>
-          <t>link_9_url</t>
-        </is>
-      </c>
-      <c r="BJ1" t="inlineStr">
-        <is>
-          <t>link_9_desc</t>
-        </is>
-      </c>
-      <c r="BK1" t="inlineStr">
-        <is>
-          <t>link_9_media</t>
-        </is>
-      </c>
-      <c r="BL1" t="inlineStr">
-        <is>
-          <t>link_9_enabled</t>
-        </is>
-      </c>
-      <c r="BM1" t="inlineStr">
-        <is>
-          <t>link_10_id</t>
-        </is>
-      </c>
-      <c r="BN1" t="inlineStr">
-        <is>
-          <t>link_10_name</t>
-        </is>
-      </c>
-      <c r="BO1" t="inlineStr">
-        <is>
           <t>link_10_url</t>
-        </is>
-      </c>
-      <c r="BP1" t="inlineStr">
-        <is>
-          <t>link_10_desc</t>
-        </is>
-      </c>
-      <c r="BQ1" t="inlineStr">
-        <is>
-          <t>link_10_media</t>
-        </is>
-      </c>
-      <c r="BR1" t="inlineStr">
-        <is>
-          <t>link_10_enabled</t>
-        </is>
-      </c>
-      <c r="BS1" t="inlineStr">
-        <is>
-          <t>source_1_name</t>
-        </is>
-      </c>
-      <c r="BT1" t="inlineStr">
-        <is>
-          <t>source_1_url</t>
-        </is>
-      </c>
-      <c r="BU1" t="inlineStr">
-        <is>
-          <t>source_2_name</t>
-        </is>
-      </c>
-      <c r="BV1" t="inlineStr">
-        <is>
-          <t>source_2_url</t>
-        </is>
-      </c>
-      <c r="BW1" t="inlineStr">
-        <is>
-          <t>source_3_name</t>
-        </is>
-      </c>
-      <c r="BX1" t="inlineStr">
-        <is>
-          <t>source_3_url</t>
-        </is>
-      </c>
-      <c r="BY1" t="inlineStr">
-        <is>
-          <t>source_4_name</t>
-        </is>
-      </c>
-      <c r="BZ1" t="inlineStr">
-        <is>
-          <t>source_4_url</t>
-        </is>
-      </c>
-      <c r="CA1" t="inlineStr">
-        <is>
-          <t>source_5_name</t>
-        </is>
-      </c>
-      <c r="CB1" t="inlineStr">
-        <is>
-          <t>source_5_url</t>
         </is>
       </c>
     </row>
@@ -822,25 +1203,25 @@
       <c r="A2" t="n">
         <v>0</v>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>全国</t>
         </is>
       </c>
-      <c r="D2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E2" t="inlineStr">
+      <c r="E2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" t="inlineStr">
         <is>
           <t>全国人民代表大会</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>最高国家权力机关，行使国家立法权，官方网站发布法律、公报与常委会信息。</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>人大,全国人大,国家立法</t>
         </is>
@@ -853,26 +1234,6 @@
       <c r="M2" t="inlineStr">
         <is>
           <t>https://www.npc.gov.cn</t>
-        </is>
-      </c>
-      <c r="BS2" t="inlineStr">
-        <is>
-          <t>百度百科</t>
-        </is>
-      </c>
-      <c r="BT2" t="inlineStr">
-        <is>
-          <t>https://baike.baidu.com/item/%E5%85%A8%E5%9B%BD%E4%BA%BA%E6%B0%91%E4%BB%A3%E8%A1%A8%E5%A4%A7%E4%BC%9A</t>
-        </is>
-      </c>
-      <c r="BU2" t="inlineStr">
-        <is>
-          <t>中国政府网</t>
-        </is>
-      </c>
-      <c r="BV2" t="inlineStr">
-        <is>
-          <t>https://www.gov.cn</t>
         </is>
       </c>
     </row>
@@ -880,25 +1241,25 @@
       <c r="A3" t="n">
         <v>1</v>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>直辖市</t>
         </is>
       </c>
-      <c r="D3" t="n">
-        <v>1</v>
-      </c>
-      <c r="E3" t="inlineStr">
+      <c r="E3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F3" t="inlineStr">
         <is>
           <t>北京市人民代表大会常务委员会</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>北京市人民代表大会常设机关，发布地方立法、监督与代表工作信息。</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>人大,北京,直辖市</t>
         </is>
@@ -911,16 +1272,6 @@
       <c r="M3" t="inlineStr">
         <is>
           <t>https://www.bjrd.gov.cn</t>
-        </is>
-      </c>
-      <c r="BS3" t="inlineStr">
-        <is>
-          <t>百度百科</t>
-        </is>
-      </c>
-      <c r="BT3" t="inlineStr">
-        <is>
-          <t>https://baike.baidu.com/item/%E5%8C%97%E4%BA%AC%E5%B8%82%E4%BA%BA%E6%B0%91%E4%BB%A3%E8%A1%A8%E5%A4%A7%E4%BC%9A%E5%B8%B8%E5%8A%A1%E5%A7%94%E5%91%98%E4%BC%9A</t>
         </is>
       </c>
     </row>
@@ -928,25 +1279,25 @@
       <c r="A4" t="n">
         <v>2</v>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>直辖市</t>
         </is>
       </c>
-      <c r="D4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E4" t="inlineStr">
+      <c r="E4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" t="inlineStr">
         <is>
           <t>上海市人民代表大会常务委员会</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>上海市人民代表大会常设机关，地方立法与监督工作平台。</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>人大,上海,直辖市</t>
         </is>
@@ -959,16 +1310,6 @@
       <c r="M4" t="inlineStr">
         <is>
           <t>https://www.shrd.gov.cn</t>
-        </is>
-      </c>
-      <c r="BS4" t="inlineStr">
-        <is>
-          <t>百度百科</t>
-        </is>
-      </c>
-      <c r="BT4" t="inlineStr">
-        <is>
-          <t>https://baike.baidu.com/item/%E4%B8%8A%E6%B5%B7%E5%B8%82%E4%BA%BA%E6%B0%91%E4%BB%A3%E8%A1%A8%E5%A4%A7%E4%BC%9A%E5%B8%B8%E5%8A%A1%E5%A7%94%E5%91%98%E4%BC%9A</t>
         </is>
       </c>
     </row>
@@ -976,25 +1317,25 @@
       <c r="A5" t="n">
         <v>3</v>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>直辖市</t>
         </is>
       </c>
-      <c r="D5" t="n">
-        <v>1</v>
-      </c>
-      <c r="E5" t="inlineStr">
+      <c r="E5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" t="inlineStr">
         <is>
           <t>天津市人民代表大会常务委员会</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>天津市人民代表大会常设机关，发布地方性法规与监督信息。</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>人大,天津,直辖市</t>
         </is>
@@ -1014,25 +1355,25 @@
       <c r="A6" t="n">
         <v>4</v>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>直辖市</t>
         </is>
       </c>
-      <c r="D6" t="n">
-        <v>1</v>
-      </c>
-      <c r="E6" t="inlineStr">
+      <c r="E6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" t="inlineStr">
         <is>
           <t>重庆市人民代表大会常务委员会</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>重庆市人民代表大会常设机关，地方立法与代表工作平台。</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>人大,重庆,直辖市</t>
         </is>
@@ -1052,25 +1393,25 @@
       <c r="A7" t="n">
         <v>5</v>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>省</t>
         </is>
       </c>
-      <c r="D7" t="n">
-        <v>1</v>
-      </c>
-      <c r="E7" t="inlineStr">
+      <c r="E7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" t="inlineStr">
         <is>
           <t>河北省人民代表大会常务委员会</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>河北省人民代表大会常设机关，发布地方立法、监督与代表履职信息。</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>人大,河北,省</t>
         </is>
@@ -1090,25 +1431,25 @@
       <c r="A8" t="n">
         <v>6</v>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>省</t>
         </is>
       </c>
-      <c r="D8" t="n">
-        <v>1</v>
-      </c>
-      <c r="E8" t="inlineStr">
+      <c r="E8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F8" t="inlineStr">
         <is>
           <t>山西省人民代表大会常务委员会</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>山西省人民代表大会常设机关，发布地方性法规与监督工作信息。</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t>人大,山西,省</t>
         </is>
@@ -1128,25 +1469,25 @@
       <c r="A9" t="n">
         <v>7</v>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>省</t>
         </is>
       </c>
-      <c r="D9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E9" t="inlineStr">
+      <c r="E9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" t="inlineStr">
         <is>
           <t>辽宁省人民代表大会常务委员会</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>辽宁省人民代表大会常设机关，发布地方立法与代表工作信息。</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t>人大,辽宁,省</t>
         </is>
@@ -1166,25 +1507,25 @@
       <c r="A10" t="n">
         <v>8</v>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>省</t>
         </is>
       </c>
-      <c r="D10" t="n">
-        <v>1</v>
-      </c>
-      <c r="E10" t="inlineStr">
+      <c r="E10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" t="inlineStr">
         <is>
           <t>吉林省人民代表大会常务委员会</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>吉林省人民代表大会常设机关，发布地方性法规与监督信息。</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t>人大,吉林,省</t>
         </is>
@@ -1204,25 +1545,25 @@
       <c r="A11" t="n">
         <v>9</v>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>省</t>
         </is>
       </c>
-      <c r="D11" t="n">
-        <v>1</v>
-      </c>
-      <c r="E11" t="inlineStr">
+      <c r="E11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" t="inlineStr">
         <is>
           <t>黑龙江省人民代表大会常务委员会</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>黑龙江省人民代表大会常设机关，发布地方立法、监督与代表工作信息。</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t>人大,黑龙江,省</t>
         </is>
@@ -1242,25 +1583,25 @@
       <c r="A12" t="n">
         <v>10</v>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>省</t>
         </is>
       </c>
-      <c r="D12" t="n">
-        <v>1</v>
-      </c>
-      <c r="E12" t="inlineStr">
+      <c r="E12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" t="inlineStr">
         <is>
           <t>江苏省人民代表大会常务委员会</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>江苏省人民代表大会常设机关，地方立法与监督工作平台。</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t>人大,江苏,省</t>
         </is>
@@ -1280,25 +1621,25 @@
       <c r="A13" t="n">
         <v>11</v>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>省</t>
         </is>
       </c>
-      <c r="D13" t="n">
-        <v>1</v>
-      </c>
-      <c r="E13" t="inlineStr">
+      <c r="E13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F13" t="inlineStr">
         <is>
           <t>浙江省人民代表大会常务委员会</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>浙江省人民代表大会常设机关，发布地方性法规与代表信息。</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t>人大,浙江,省</t>
         </is>
@@ -1318,25 +1659,25 @@
       <c r="A14" t="n">
         <v>12</v>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>省</t>
         </is>
       </c>
-      <c r="D14" t="n">
-        <v>1</v>
-      </c>
-      <c r="E14" t="inlineStr">
+      <c r="E14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F14" t="inlineStr">
         <is>
           <t>安徽省人民代表大会常务委员会</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>安徽省人民代表大会常设机关，发布地方立法与代表履职信息。</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="I14" t="inlineStr">
         <is>
           <t>人大,安徽,省</t>
         </is>
@@ -1356,25 +1697,25 @@
       <c r="A15" t="n">
         <v>13</v>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>省</t>
         </is>
       </c>
-      <c r="D15" t="n">
-        <v>1</v>
-      </c>
-      <c r="E15" t="inlineStr">
+      <c r="E15" t="n">
+        <v>1</v>
+      </c>
+      <c r="F15" t="inlineStr">
         <is>
           <t>福建省人民代表大会常务委员会</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>福建省人民代表大会常设机关，发布地方性法规与监督工作信息。</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="I15" t="inlineStr">
         <is>
           <t>人大,福建,省</t>
         </is>
@@ -1394,25 +1735,25 @@
       <c r="A16" t="n">
         <v>14</v>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>省</t>
         </is>
       </c>
-      <c r="D16" t="n">
-        <v>1</v>
-      </c>
-      <c r="E16" t="inlineStr">
+      <c r="E16" t="n">
+        <v>1</v>
+      </c>
+      <c r="F16" t="inlineStr">
         <is>
           <t>江西省人民代表大会常务委员会</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>江西省人民代表大会常设机关，发布地方立法与代表工作信息。</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="I16" t="inlineStr">
         <is>
           <t>人大,江西,省</t>
         </is>
@@ -1432,25 +1773,25 @@
       <c r="A17" t="n">
         <v>15</v>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>省</t>
         </is>
       </c>
-      <c r="D17" t="n">
-        <v>1</v>
-      </c>
-      <c r="E17" t="inlineStr">
+      <c r="E17" t="n">
+        <v>1</v>
+      </c>
+      <c r="F17" t="inlineStr">
         <is>
           <t>山东省人民代表大会常务委员会</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>山东省人民代表大会常设机关，地方立法与监督工作平台。</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="I17" t="inlineStr">
         <is>
           <t>人大,山东,省</t>
         </is>
@@ -1470,25 +1811,25 @@
       <c r="A18" t="n">
         <v>16</v>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>省</t>
         </is>
       </c>
-      <c r="D18" t="n">
-        <v>1</v>
-      </c>
-      <c r="E18" t="inlineStr">
+      <c r="E18" t="n">
+        <v>1</v>
+      </c>
+      <c r="F18" t="inlineStr">
         <is>
           <t>河南省人民代表大会常务委员会</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>河南省人民代表大会常设机关，发布地方性法规与监督信息。</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="I18" t="inlineStr">
         <is>
           <t>人大,河南,省</t>
         </is>
@@ -1508,25 +1849,25 @@
       <c r="A19" t="n">
         <v>17</v>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>省</t>
         </is>
       </c>
-      <c r="D19" t="n">
-        <v>1</v>
-      </c>
-      <c r="E19" t="inlineStr">
+      <c r="E19" t="n">
+        <v>1</v>
+      </c>
+      <c r="F19" t="inlineStr">
         <is>
           <t>湖北省人民代表大会常务委员会</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t>湖北省人民代表大会常设机关，地方立法与代表工作平台。</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
+      <c r="I19" t="inlineStr">
         <is>
           <t>人大,湖北,省</t>
         </is>
@@ -1546,25 +1887,25 @@
       <c r="A20" t="n">
         <v>18</v>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>省</t>
         </is>
       </c>
-      <c r="D20" t="n">
-        <v>1</v>
-      </c>
-      <c r="E20" t="inlineStr">
+      <c r="E20" t="n">
+        <v>1</v>
+      </c>
+      <c r="F20" t="inlineStr">
         <is>
           <t>湖南省人民代表大会常务委员会</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="G20" t="inlineStr">
         <is>
           <t>湖南省人民代表大会常设机关，发布地方性法规与监督信息。</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
+      <c r="I20" t="inlineStr">
         <is>
           <t>人大,湖南,省</t>
         </is>
@@ -1584,25 +1925,25 @@
       <c r="A21" t="n">
         <v>19</v>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t>省</t>
         </is>
       </c>
-      <c r="D21" t="n">
-        <v>1</v>
-      </c>
-      <c r="E21" t="inlineStr">
+      <c r="E21" t="n">
+        <v>1</v>
+      </c>
+      <c r="F21" t="inlineStr">
         <is>
           <t>广东省人民代表大会常务委员会</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="G21" t="inlineStr">
         <is>
           <t>广东省人民代表大会常设机关，发布地方性法规与监督信息。</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
+      <c r="I21" t="inlineStr">
         <is>
           <t>人大,广东,省</t>
         </is>
@@ -1622,25 +1963,25 @@
       <c r="A22" t="n">
         <v>20</v>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="D22" t="inlineStr">
         <is>
           <t>省</t>
         </is>
       </c>
-      <c r="D22" t="n">
-        <v>1</v>
-      </c>
-      <c r="E22" t="inlineStr">
+      <c r="E22" t="n">
+        <v>1</v>
+      </c>
+      <c r="F22" t="inlineStr">
         <is>
           <t>海南省人民代表大会常务委员会</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t>海南省人民代表大会常设机关，发布地方立法、监督与代表工作信息。</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
+      <c r="I22" t="inlineStr">
         <is>
           <t>人大,海南,省</t>
         </is>
@@ -1660,25 +2001,25 @@
       <c r="A23" t="n">
         <v>21</v>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="D23" t="inlineStr">
         <is>
           <t>省</t>
         </is>
       </c>
-      <c r="D23" t="n">
-        <v>1</v>
-      </c>
-      <c r="E23" t="inlineStr">
+      <c r="E23" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" t="inlineStr">
         <is>
           <t>四川省人民代表大会常务委员会</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="G23" t="inlineStr">
         <is>
           <t>四川省人民代表大会常设机关，发布地方性法规与监督信息。</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
+      <c r="I23" t="inlineStr">
         <is>
           <t>人大,四川,省</t>
         </is>
@@ -1698,25 +2039,25 @@
       <c r="A24" t="n">
         <v>22</v>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="D24" t="inlineStr">
         <is>
           <t>省</t>
         </is>
       </c>
-      <c r="D24" t="n">
-        <v>1</v>
-      </c>
-      <c r="E24" t="inlineStr">
+      <c r="E24" t="n">
+        <v>1</v>
+      </c>
+      <c r="F24" t="inlineStr">
         <is>
           <t>贵州省人民代表大会常务委员会</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="G24" t="inlineStr">
         <is>
           <t>贵州省人民代表大会常设机关，发布地方性法规与监督信息。</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
+      <c r="I24" t="inlineStr">
         <is>
           <t>人大,贵州,省</t>
         </is>
@@ -1736,25 +2077,25 @@
       <c r="A25" t="n">
         <v>23</v>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="D25" t="inlineStr">
         <is>
           <t>省</t>
         </is>
       </c>
-      <c r="D25" t="n">
-        <v>1</v>
-      </c>
-      <c r="E25" t="inlineStr">
+      <c r="E25" t="n">
+        <v>1</v>
+      </c>
+      <c r="F25" t="inlineStr">
         <is>
           <t>云南省人民代表大会常务委员会</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="G25" t="inlineStr">
         <is>
           <t>云南省人民代表大会常设机关，发布地方立法与代表履职信息。</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
+      <c r="I25" t="inlineStr">
         <is>
           <t>人大,云南,省</t>
         </is>
@@ -1774,25 +2115,25 @@
       <c r="A26" t="n">
         <v>24</v>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="D26" t="inlineStr">
         <is>
           <t>省</t>
         </is>
       </c>
-      <c r="D26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E26" t="inlineStr">
+      <c r="E26" t="n">
+        <v>1</v>
+      </c>
+      <c r="F26" t="inlineStr">
         <is>
           <t>陕西省人民代表大会常务委员会</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="G26" t="inlineStr">
         <is>
           <t>陕西省人民代表大会常设机关，发布地方性法规与监督工作信息。</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
+      <c r="I26" t="inlineStr">
         <is>
           <t>人大,陕西,省</t>
         </is>
@@ -1812,25 +2153,25 @@
       <c r="A27" t="n">
         <v>25</v>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="D27" t="inlineStr">
         <is>
           <t>省</t>
         </is>
       </c>
-      <c r="D27" t="n">
-        <v>1</v>
-      </c>
-      <c r="E27" t="inlineStr">
+      <c r="E27" t="n">
+        <v>1</v>
+      </c>
+      <c r="F27" t="inlineStr">
         <is>
           <t>甘肃省人民代表大会常务委员会</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
+      <c r="G27" t="inlineStr">
         <is>
           <t>甘肃省人民代表大会常设机关，发布地方立法与代表工作信息。</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
+      <c r="I27" t="inlineStr">
         <is>
           <t>人大,甘肃,省</t>
         </is>
@@ -1850,25 +2191,25 @@
       <c r="A28" t="n">
         <v>26</v>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="D28" t="inlineStr">
         <is>
           <t>省</t>
         </is>
       </c>
-      <c r="D28" t="n">
-        <v>1</v>
-      </c>
-      <c r="E28" t="inlineStr">
+      <c r="E28" t="n">
+        <v>1</v>
+      </c>
+      <c r="F28" t="inlineStr">
         <is>
           <t>青海省人民代表大会常务委员会</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
+      <c r="G28" t="inlineStr">
         <is>
           <t>青海省人民代表大会常设机关，发布地方性法规与监督信息。</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
+      <c r="I28" t="inlineStr">
         <is>
           <t>人大,青海,省</t>
         </is>
@@ -1888,25 +2229,25 @@
       <c r="A29" t="n">
         <v>27</v>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="D29" t="inlineStr">
         <is>
           <t>自治区</t>
         </is>
       </c>
-      <c r="D29" t="n">
-        <v>1</v>
-      </c>
-      <c r="E29" t="inlineStr">
+      <c r="E29" t="n">
+        <v>1</v>
+      </c>
+      <c r="F29" t="inlineStr">
         <is>
           <t>内蒙古自治区人民代表大会常务委员会</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
+      <c r="G29" t="inlineStr">
         <is>
           <t>内蒙古自治区人民代表大会常设机关，发布地方立法、监督与代表工作信息。</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
+      <c r="I29" t="inlineStr">
         <is>
           <t>人大,内蒙古,自治区</t>
         </is>
@@ -1926,25 +2267,25 @@
       <c r="A30" t="n">
         <v>28</v>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="D30" t="inlineStr">
         <is>
           <t>自治区</t>
         </is>
       </c>
-      <c r="D30" t="n">
-        <v>1</v>
-      </c>
-      <c r="E30" t="inlineStr">
+      <c r="E30" t="n">
+        <v>1</v>
+      </c>
+      <c r="F30" t="inlineStr">
         <is>
           <t>广西壮族自治区人民代表大会常务委员会</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
+      <c r="G30" t="inlineStr">
         <is>
           <t>广西壮族自治区人民代表大会常设机关，发布地方立法与代表履职信息。</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
+      <c r="I30" t="inlineStr">
         <is>
           <t>人大,广西,自治区</t>
         </is>
@@ -1964,25 +2305,25 @@
       <c r="A31" t="n">
         <v>29</v>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="D31" t="inlineStr">
         <is>
           <t>自治区</t>
         </is>
       </c>
-      <c r="D31" t="n">
-        <v>1</v>
-      </c>
-      <c r="E31" t="inlineStr">
+      <c r="E31" t="n">
+        <v>1</v>
+      </c>
+      <c r="F31" t="inlineStr">
         <is>
           <t>西藏自治区人民代表大会常务委员会</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
+      <c r="G31" t="inlineStr">
         <is>
           <t>西藏自治区人民代表大会常设机关，发布地方立法与监督信息。</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
+      <c r="I31" t="inlineStr">
         <is>
           <t>人大,西藏,自治区</t>
         </is>
@@ -2002,25 +2343,25 @@
       <c r="A32" t="n">
         <v>30</v>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="D32" t="inlineStr">
         <is>
           <t>自治区</t>
         </is>
       </c>
-      <c r="D32" t="n">
-        <v>1</v>
-      </c>
-      <c r="E32" t="inlineStr">
+      <c r="E32" t="n">
+        <v>1</v>
+      </c>
+      <c r="F32" t="inlineStr">
         <is>
           <t>宁夏回族自治区人民代表大会常务委员会</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
+      <c r="G32" t="inlineStr">
         <is>
           <t>宁夏回族自治区人民代表大会常设机关，发布地方性法规与代表工作信息。</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
+      <c r="I32" t="inlineStr">
         <is>
           <t>人大,宁夏,自治区</t>
         </is>
@@ -2040,25 +2381,25 @@
       <c r="A33" t="n">
         <v>31</v>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="D33" t="inlineStr">
         <is>
           <t>自治区</t>
         </is>
       </c>
-      <c r="D33" t="n">
-        <v>1</v>
-      </c>
-      <c r="E33" t="inlineStr">
+      <c r="E33" t="n">
+        <v>1</v>
+      </c>
+      <c r="F33" t="inlineStr">
         <is>
           <t>新疆维吾尔自治区人民代表大会常务委员会</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
+      <c r="G33" t="inlineStr">
         <is>
           <t>新疆维吾尔自治区人民代表大会常设机关，发布地方立法、监督与代表工作信息。</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
+      <c r="I33" t="inlineStr">
         <is>
           <t>人大,新疆,自治区</t>
         </is>
@@ -2078,25 +2419,25 @@
       <c r="A34" t="n">
         <v>32</v>
       </c>
-      <c r="C34" t="inlineStr">
+      <c r="D34" t="inlineStr">
         <is>
           <t>国务院</t>
         </is>
       </c>
-      <c r="D34" t="n">
-        <v>1</v>
-      </c>
-      <c r="E34" t="inlineStr">
+      <c r="E34" t="n">
+        <v>1</v>
+      </c>
+      <c r="F34" t="inlineStr">
         <is>
           <t>中华人民共和国中央人民政府（国务院）</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
+      <c r="G34" t="inlineStr">
         <is>
           <t>国务院官方网站，国家政务总门户，发布政策法规与政务信息。</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
+      <c r="I34" t="inlineStr">
         <is>
           <t>政务,国务院,中央政府</t>
         </is>
@@ -2116,25 +2457,25 @@
       <c r="A35" t="n">
         <v>33</v>
       </c>
-      <c r="C35" t="inlineStr">
+      <c r="D35" t="inlineStr">
         <is>
           <t>国家平台</t>
         </is>
       </c>
-      <c r="D35" t="n">
-        <v>1</v>
-      </c>
-      <c r="E35" t="inlineStr">
+      <c r="E35" t="n">
+        <v>1</v>
+      </c>
+      <c r="F35" t="inlineStr">
         <is>
           <t>国家政务服务平台</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
+      <c r="G35" t="inlineStr">
         <is>
           <t>全国统一政务服务平台，提供在线办事、政务服务与效能监督。</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
+      <c r="I35" t="inlineStr">
         <is>
           <t>政务,服务平台,在线办事</t>
         </is>
@@ -2154,25 +2495,25 @@
       <c r="A36" t="n">
         <v>34</v>
       </c>
-      <c r="C36" t="inlineStr">
+      <c r="D36" t="inlineStr">
         <is>
           <t>组成部门</t>
         </is>
       </c>
-      <c r="D36" t="n">
-        <v>1</v>
-      </c>
-      <c r="E36" t="inlineStr">
+      <c r="E36" t="n">
+        <v>1</v>
+      </c>
+      <c r="F36" t="inlineStr">
         <is>
           <t>外交部</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
+      <c r="G36" t="inlineStr">
         <is>
           <t>主管外交事务，发布外交政策、双边关系与国际交往信息。</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
+      <c r="I36" t="inlineStr">
         <is>
           <t>政务,外交,外交部</t>
         </is>
@@ -2192,25 +2533,25 @@
       <c r="A37" t="n">
         <v>35</v>
       </c>
-      <c r="C37" t="inlineStr">
+      <c r="D37" t="inlineStr">
         <is>
           <t>组成部门</t>
         </is>
       </c>
-      <c r="D37" t="n">
-        <v>1</v>
-      </c>
-      <c r="E37" t="inlineStr">
+      <c r="E37" t="n">
+        <v>1</v>
+      </c>
+      <c r="F37" t="inlineStr">
         <is>
           <t>国防部</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
+      <c r="G37" t="inlineStr">
         <is>
           <t>中华人民共和国国防部，发布国防政策、军队建设与权威军事信息。</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
+      <c r="I37" t="inlineStr">
         <is>
           <t>政务,国防,国防部</t>
         </is>
@@ -2230,25 +2571,25 @@
       <c r="A38" t="n">
         <v>36</v>
       </c>
-      <c r="C38" t="inlineStr">
+      <c r="D38" t="inlineStr">
         <is>
           <t>组成部门</t>
         </is>
       </c>
-      <c r="D38" t="n">
-        <v>1</v>
-      </c>
-      <c r="E38" t="inlineStr">
+      <c r="E38" t="n">
+        <v>1</v>
+      </c>
+      <c r="F38" t="inlineStr">
         <is>
           <t>国家发展和改革委员会</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
+      <c r="G38" t="inlineStr">
         <is>
           <t>宏观经济综合管理，拟订发展战略与规划。</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
+      <c r="I38" t="inlineStr">
         <is>
           <t>政务,发改委,宏观经济</t>
         </is>
@@ -2268,25 +2609,25 @@
       <c r="A39" t="n">
         <v>37</v>
       </c>
-      <c r="C39" t="inlineStr">
+      <c r="D39" t="inlineStr">
         <is>
           <t>组成部门</t>
         </is>
       </c>
-      <c r="D39" t="n">
-        <v>1</v>
-      </c>
-      <c r="E39" t="inlineStr">
+      <c r="E39" t="n">
+        <v>1</v>
+      </c>
+      <c r="F39" t="inlineStr">
         <is>
           <t>教育部</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
+      <c r="G39" t="inlineStr">
         <is>
           <t>主管教育事业与语言文字工作，发布教育政策。</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
+      <c r="I39" t="inlineStr">
         <is>
           <t>政务,教育,教育部</t>
         </is>
@@ -2306,25 +2647,25 @@
       <c r="A40" t="n">
         <v>38</v>
       </c>
-      <c r="C40" t="inlineStr">
+      <c r="D40" t="inlineStr">
         <is>
           <t>组成部门</t>
         </is>
       </c>
-      <c r="D40" t="n">
-        <v>1</v>
-      </c>
-      <c r="E40" t="inlineStr">
+      <c r="E40" t="n">
+        <v>1</v>
+      </c>
+      <c r="F40" t="inlineStr">
         <is>
           <t>科学技术部</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
+      <c r="G40" t="inlineStr">
         <is>
           <t>主管科技发展与创新，发布科技政策与研发计划信息。</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
+      <c r="I40" t="inlineStr">
         <is>
           <t>政务,科技,科技部</t>
         </is>
@@ -2344,25 +2685,25 @@
       <c r="A41" t="n">
         <v>39</v>
       </c>
-      <c r="C41" t="inlineStr">
+      <c r="D41" t="inlineStr">
         <is>
           <t>组成部门</t>
         </is>
       </c>
-      <c r="D41" t="n">
-        <v>1</v>
-      </c>
-      <c r="E41" t="inlineStr">
+      <c r="E41" t="n">
+        <v>1</v>
+      </c>
+      <c r="F41" t="inlineStr">
         <is>
           <t>工业和信息化部</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
+      <c r="G41" t="inlineStr">
         <is>
           <t>主管工业与信息化产业发展与行业管理。</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
+      <c r="I41" t="inlineStr">
         <is>
           <t>政务,工信,信息化</t>
         </is>
@@ -2382,25 +2723,25 @@
       <c r="A42" t="n">
         <v>40</v>
       </c>
-      <c r="C42" t="inlineStr">
+      <c r="D42" t="inlineStr">
         <is>
           <t>组成部门</t>
         </is>
       </c>
-      <c r="D42" t="n">
-        <v>1</v>
-      </c>
-      <c r="E42" t="inlineStr">
+      <c r="E42" t="n">
+        <v>1</v>
+      </c>
+      <c r="F42" t="inlineStr">
         <is>
           <t>国家民族事务委员会</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
+      <c r="G42" t="inlineStr">
         <is>
           <t>主管民族事务与民族团结进步工作，发布民族政策信息。</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
+      <c r="I42" t="inlineStr">
         <is>
           <t>政务,民委,民族事务</t>
         </is>
@@ -2420,25 +2761,25 @@
       <c r="A43" t="n">
         <v>41</v>
       </c>
-      <c r="C43" t="inlineStr">
+      <c r="D43" t="inlineStr">
         <is>
           <t>组成部门</t>
         </is>
       </c>
-      <c r="D43" t="n">
-        <v>1</v>
-      </c>
-      <c r="E43" t="inlineStr">
+      <c r="E43" t="n">
+        <v>1</v>
+      </c>
+      <c r="F43" t="inlineStr">
         <is>
           <t>公安部</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
+      <c r="G43" t="inlineStr">
         <is>
           <t>维护社会治安，主管公安工作。</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
+      <c r="I43" t="inlineStr">
         <is>
           <t>政务,公安,公安部</t>
         </is>
@@ -2458,25 +2799,25 @@
       <c r="A44" t="n">
         <v>42</v>
       </c>
-      <c r="C44" t="inlineStr">
+      <c r="D44" t="inlineStr">
         <is>
           <t>组成部门</t>
         </is>
       </c>
-      <c r="D44" t="n">
-        <v>1</v>
-      </c>
-      <c r="E44" t="inlineStr">
+      <c r="E44" t="n">
+        <v>1</v>
+      </c>
+      <c r="F44" t="inlineStr">
         <is>
           <t>民政部</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr">
+      <c r="G44" t="inlineStr">
         <is>
           <t>主管民政事务、社会救助与社会组织管理。</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
+      <c r="I44" t="inlineStr">
         <is>
           <t>政务,民政,民政部</t>
         </is>
@@ -2496,25 +2837,25 @@
       <c r="A45" t="n">
         <v>43</v>
       </c>
-      <c r="C45" t="inlineStr">
+      <c r="D45" t="inlineStr">
         <is>
           <t>组成部门</t>
         </is>
       </c>
-      <c r="D45" t="n">
-        <v>1</v>
-      </c>
-      <c r="E45" t="inlineStr">
+      <c r="E45" t="n">
+        <v>1</v>
+      </c>
+      <c r="F45" t="inlineStr">
         <is>
           <t>司法部</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
+      <c r="G45" t="inlineStr">
         <is>
           <t>主管司法行政、法治建设与法律服务。</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
+      <c r="I45" t="inlineStr">
         <is>
           <t>政务,司法,司法部</t>
         </is>
@@ -2534,25 +2875,25 @@
       <c r="A46" t="n">
         <v>44</v>
       </c>
-      <c r="C46" t="inlineStr">
+      <c r="D46" t="inlineStr">
         <is>
           <t>组成部门</t>
         </is>
       </c>
-      <c r="D46" t="n">
-        <v>1</v>
-      </c>
-      <c r="E46" t="inlineStr">
+      <c r="E46" t="n">
+        <v>1</v>
+      </c>
+      <c r="F46" t="inlineStr">
         <is>
           <t>财政部</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
+      <c r="G46" t="inlineStr">
         <is>
           <t>主管国家财政收支与财税政策。</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
+      <c r="I46" t="inlineStr">
         <is>
           <t>政务,财政,财政部</t>
         </is>
@@ -2572,25 +2913,25 @@
       <c r="A47" t="n">
         <v>45</v>
       </c>
-      <c r="C47" t="inlineStr">
+      <c r="D47" t="inlineStr">
         <is>
           <t>组成部门</t>
         </is>
       </c>
-      <c r="D47" t="n">
-        <v>1</v>
-      </c>
-      <c r="E47" t="inlineStr">
+      <c r="E47" t="n">
+        <v>1</v>
+      </c>
+      <c r="F47" t="inlineStr">
         <is>
           <t>人力资源和社会保障部</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr">
+      <c r="G47" t="inlineStr">
         <is>
           <t>主管就业、社保与人事人才工作。</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
+      <c r="I47" t="inlineStr">
         <is>
           <t>政务,人社,社保</t>
         </is>
@@ -2610,25 +2951,25 @@
       <c r="A48" t="n">
         <v>46</v>
       </c>
-      <c r="C48" t="inlineStr">
+      <c r="D48" t="inlineStr">
         <is>
           <t>组成部门</t>
         </is>
       </c>
-      <c r="D48" t="n">
-        <v>1</v>
-      </c>
-      <c r="E48" t="inlineStr">
+      <c r="E48" t="n">
+        <v>1</v>
+      </c>
+      <c r="F48" t="inlineStr">
         <is>
           <t>自然资源部</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr">
+      <c r="G48" t="inlineStr">
         <is>
           <t>主管自然资源调查、规划与确权登记。</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
+      <c r="I48" t="inlineStr">
         <is>
           <t>政务,自然资源,国土</t>
         </is>
@@ -2648,25 +2989,25 @@
       <c r="A49" t="n">
         <v>47</v>
       </c>
-      <c r="C49" t="inlineStr">
+      <c r="D49" t="inlineStr">
         <is>
           <t>组成部门</t>
         </is>
       </c>
-      <c r="D49" t="n">
-        <v>1</v>
-      </c>
-      <c r="E49" t="inlineStr">
+      <c r="E49" t="n">
+        <v>1</v>
+      </c>
+      <c r="F49" t="inlineStr">
         <is>
           <t>生态环境部</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr">
+      <c r="G49" t="inlineStr">
         <is>
           <t>主管生态环境保护的监督管理。</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
+      <c r="I49" t="inlineStr">
         <is>
           <t>政务,生态环境,环保</t>
         </is>
@@ -2686,25 +3027,25 @@
       <c r="A50" t="n">
         <v>48</v>
       </c>
-      <c r="C50" t="inlineStr">
+      <c r="D50" t="inlineStr">
         <is>
           <t>组成部门</t>
         </is>
       </c>
-      <c r="D50" t="n">
-        <v>1</v>
-      </c>
-      <c r="E50" t="inlineStr">
+      <c r="E50" t="n">
+        <v>1</v>
+      </c>
+      <c r="F50" t="inlineStr">
         <is>
           <t>住房和城乡建设部</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr">
+      <c r="G50" t="inlineStr">
         <is>
           <t>主管住房保障与城乡建设，发布建筑市场与市政建设政策。</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
+      <c r="I50" t="inlineStr">
         <is>
           <t>政务,住建,城乡建设</t>
         </is>
@@ -2724,25 +3065,25 @@
       <c r="A51" t="n">
         <v>49</v>
       </c>
-      <c r="C51" t="inlineStr">
+      <c r="D51" t="inlineStr">
         <is>
           <t>组成部门</t>
         </is>
       </c>
-      <c r="D51" t="n">
-        <v>1</v>
-      </c>
-      <c r="E51" t="inlineStr">
+      <c r="E51" t="n">
+        <v>1</v>
+      </c>
+      <c r="F51" t="inlineStr">
         <is>
           <t>交通运输部</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr">
+      <c r="G51" t="inlineStr">
         <is>
           <t>主管公路、水路、铁路等综合交通运输。</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
+      <c r="I51" t="inlineStr">
         <is>
           <t>政务,交通,运输</t>
         </is>
@@ -2762,25 +3103,25 @@
       <c r="A52" t="n">
         <v>50</v>
       </c>
-      <c r="C52" t="inlineStr">
+      <c r="D52" t="inlineStr">
         <is>
           <t>组成部门</t>
         </is>
       </c>
-      <c r="D52" t="n">
-        <v>1</v>
-      </c>
-      <c r="E52" t="inlineStr">
+      <c r="E52" t="n">
+        <v>1</v>
+      </c>
+      <c r="F52" t="inlineStr">
         <is>
           <t>水利部</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr">
+      <c r="G52" t="inlineStr">
         <is>
           <t>主管水资源管理与水利建设，发布防汛抗旱与河湖治理信息。</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
+      <c r="I52" t="inlineStr">
         <is>
           <t>政务,水利,水资源</t>
         </is>
@@ -2800,25 +3141,25 @@
       <c r="A53" t="n">
         <v>51</v>
       </c>
-      <c r="C53" t="inlineStr">
+      <c r="D53" t="inlineStr">
         <is>
           <t>组成部门</t>
         </is>
       </c>
-      <c r="D53" t="n">
-        <v>1</v>
-      </c>
-      <c r="E53" t="inlineStr">
+      <c r="E53" t="n">
+        <v>1</v>
+      </c>
+      <c r="F53" t="inlineStr">
         <is>
           <t>农业农村部</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr">
+      <c r="G53" t="inlineStr">
         <is>
           <t>主管农业农村发展，发布乡村振兴、农业政策与农技信息。</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
+      <c r="I53" t="inlineStr">
         <is>
           <t>政务,农业,农业农村</t>
         </is>
@@ -2838,25 +3179,25 @@
       <c r="A54" t="n">
         <v>52</v>
       </c>
-      <c r="C54" t="inlineStr">
+      <c r="D54" t="inlineStr">
         <is>
           <t>组成部门</t>
         </is>
       </c>
-      <c r="D54" t="n">
-        <v>1</v>
-      </c>
-      <c r="E54" t="inlineStr">
+      <c r="E54" t="n">
+        <v>1</v>
+      </c>
+      <c r="F54" t="inlineStr">
         <is>
           <t>商务部</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr">
+      <c r="G54" t="inlineStr">
         <is>
           <t>主管国内外贸易与国际经贸合作，发布商务政策与市场信息。</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
+      <c r="I54" t="inlineStr">
         <is>
           <t>政务,商务,对外贸易</t>
         </is>
@@ -2876,25 +3217,25 @@
       <c r="A55" t="n">
         <v>53</v>
       </c>
-      <c r="C55" t="inlineStr">
+      <c r="D55" t="inlineStr">
         <is>
           <t>组成部门</t>
         </is>
       </c>
-      <c r="D55" t="n">
-        <v>1</v>
-      </c>
-      <c r="E55" t="inlineStr">
+      <c r="E55" t="n">
+        <v>1</v>
+      </c>
+      <c r="F55" t="inlineStr">
         <is>
           <t>文化和旅游部</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr">
+      <c r="G55" t="inlineStr">
         <is>
           <t>主管文化事业与旅游发展，发布文旅政策与公共服务信息。</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
+      <c r="I55" t="inlineStr">
         <is>
           <t>政务,文旅,文化旅游</t>
         </is>
@@ -2914,25 +3255,25 @@
       <c r="A56" t="n">
         <v>54</v>
       </c>
-      <c r="C56" t="inlineStr">
+      <c r="D56" t="inlineStr">
         <is>
           <t>组成部门</t>
         </is>
       </c>
-      <c r="D56" t="n">
-        <v>1</v>
-      </c>
-      <c r="E56" t="inlineStr">
+      <c r="E56" t="n">
+        <v>1</v>
+      </c>
+      <c r="F56" t="inlineStr">
         <is>
           <t>国家卫生健康委员会</t>
         </is>
       </c>
-      <c r="F56" t="inlineStr">
+      <c r="G56" t="inlineStr">
         <is>
           <t>主管国民健康与医疗卫生，发布卫生政策与健康服务信息。</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
+      <c r="I56" t="inlineStr">
         <is>
           <t>政务,卫健,卫生健康</t>
         </is>
@@ -2952,25 +3293,25 @@
       <c r="A57" t="n">
         <v>55</v>
       </c>
-      <c r="C57" t="inlineStr">
+      <c r="D57" t="inlineStr">
         <is>
           <t>组成部门</t>
         </is>
       </c>
-      <c r="D57" t="n">
-        <v>1</v>
-      </c>
-      <c r="E57" t="inlineStr">
+      <c r="E57" t="n">
+        <v>1</v>
+      </c>
+      <c r="F57" t="inlineStr">
         <is>
           <t>退役军人事务部</t>
         </is>
       </c>
-      <c r="F57" t="inlineStr">
+      <c r="G57" t="inlineStr">
         <is>
           <t>主管退役军人优抚安置与服务保障，维护军人军属权益。</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
+      <c r="I57" t="inlineStr">
         <is>
           <t>政务,退役军人,优抚安置</t>
         </is>
@@ -2990,25 +3331,25 @@
       <c r="A58" t="n">
         <v>56</v>
       </c>
-      <c r="C58" t="inlineStr">
+      <c r="D58" t="inlineStr">
         <is>
           <t>组成部门</t>
         </is>
       </c>
-      <c r="D58" t="n">
-        <v>1</v>
-      </c>
-      <c r="E58" t="inlineStr">
+      <c r="E58" t="n">
+        <v>1</v>
+      </c>
+      <c r="F58" t="inlineStr">
         <is>
           <t>应急管理部</t>
         </is>
       </c>
-      <c r="F58" t="inlineStr">
+      <c r="G58" t="inlineStr">
         <is>
           <t>主管安全生产与应急救援，发布防灾减灾与事故处置信息。</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
+      <c r="I58" t="inlineStr">
         <is>
           <t>政务,应急,安全生产</t>
         </is>
@@ -3028,25 +3369,25 @@
       <c r="A59" t="n">
         <v>57</v>
       </c>
-      <c r="C59" t="inlineStr">
+      <c r="D59" t="inlineStr">
         <is>
           <t>组成部门</t>
         </is>
       </c>
-      <c r="D59" t="n">
-        <v>1</v>
-      </c>
-      <c r="E59" t="inlineStr">
+      <c r="E59" t="n">
+        <v>1</v>
+      </c>
+      <c r="F59" t="inlineStr">
         <is>
           <t>中国人民银行</t>
         </is>
       </c>
-      <c r="F59" t="inlineStr">
+      <c r="G59" t="inlineStr">
         <is>
           <t>中央银行，制定货币政策，维护金融稳定与人民币管理。</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr">
+      <c r="I59" t="inlineStr">
         <is>
           <t>政务,央行,货币政策</t>
         </is>
@@ -3066,25 +3407,25 @@
       <c r="A60" t="n">
         <v>58</v>
       </c>
-      <c r="C60" t="inlineStr">
+      <c r="D60" t="inlineStr">
         <is>
           <t>组成部门</t>
         </is>
       </c>
-      <c r="D60" t="n">
-        <v>1</v>
-      </c>
-      <c r="E60" t="inlineStr">
+      <c r="E60" t="n">
+        <v>1</v>
+      </c>
+      <c r="F60" t="inlineStr">
         <is>
           <t>审计署</t>
         </is>
       </c>
-      <c r="F60" t="inlineStr">
+      <c r="G60" t="inlineStr">
         <is>
           <t>主管国家财政收支审计监督，发布审计结果与整改信息。</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr">
+      <c r="I60" t="inlineStr">
         <is>
           <t>政务,审计,审计监督</t>
         </is>
